--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{189DEE53-BA6A-41D9-9D2A-4E8F69458B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DECBEC7C-FBA9-4B03-948A-743FAA59251A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1770,13 +1770,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S4aH2,S2aH2,S1aH2,S3aH2</t>
+    <t>S2aH2,S4aH2,S3aH2,S1aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S1aH1,S4aH3,S2aH1,S2aH3,S3aH3,S4aH1,S1aH3,S3aH1</t>
+    <t>S2aH3,S3aH3,S4aH1,S1aH1,S4aH3,S2aH1,S1aH3,S3aH1</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S1aH1,S4aH3,S2aH1,S2aH3,S3aH3,S4aH1,S1aH3,S3aH1</v>
+        <v>S2aH3,S3aH3,S4aH1,S1aH1,S4aH3,S2aH1,S1aH3,S3aH1</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S4aH2,S2aH2,S1aH2,S3aH2</v>
+        <v>S2aH2,S4aH2,S3aH2,S1aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -2501,7 +2501,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3766C473-B8A9-4C03-8E57-ADC1F364C611}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C521BD5-5645-41AC-B786-9D2F667C1233}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2581,7 +2581,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E02FE1A9-EA9C-4128-9C41-DFEF64DB98D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCBF04FE-FB1E-4D68-957F-8AD60A91EAFA}">
   <dimension ref="B9:O1174"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -40395,7 +40395,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4468096-325B-4A2A-B206-6E437E4A9039}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECBE9103-C4A1-47AB-AD44-27444228A19B}">
   <dimension ref="B9:CI256"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -95064,7 +95064,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14DFA277-7A4E-4084-A720-670AD1112FFC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{256CD0A2-E34D-420F-8BFB-977C134115D2}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -95291,7 +95291,7 @@
         <v>46</v>
       </c>
       <c r="R14">
-        <v>0.19036666666666666</v>
+        <v>0.19036666666666668</v>
       </c>
       <c r="S14" t="s">
         <v>586</v>
@@ -95537,7 +95537,7 @@
         <v>42</v>
       </c>
       <c r="R20">
-        <v>0.24216666666666664</v>
+        <v>0.24216666666666672</v>
       </c>
       <c r="S20" t="s">
         <v>586</v>
@@ -95699,7 +95699,7 @@
         <v>46</v>
       </c>
       <c r="R26">
-        <v>0.25126666666666669</v>
+        <v>0.25126666666666664</v>
       </c>
       <c r="S26" t="s">
         <v>586</v>
@@ -95779,7 +95779,7 @@
         <v>46</v>
       </c>
       <c r="R30">
-        <v>0.22430000000000003</v>
+        <v>0.22429999999999997</v>
       </c>
       <c r="S30" t="s">
         <v>586</v>
@@ -95887,7 +95887,7 @@
         <v>42</v>
       </c>
       <c r="R36">
-        <v>0.19306666666666664</v>
+        <v>0.19306666666666669</v>
       </c>
       <c r="S36" t="s">
         <v>586</v>
@@ -96139,7 +96139,7 @@
         <v>46</v>
       </c>
       <c r="R54">
-        <v>0.21993333333333331</v>
+        <v>0.21993333333333334</v>
       </c>
       <c r="S54" t="s">
         <v>586</v>
@@ -96195,7 +96195,7 @@
         <v>46</v>
       </c>
       <c r="R58">
-        <v>0.23783333333333334</v>
+        <v>0.23783333333333331</v>
       </c>
       <c r="S58" t="s">
         <v>586</v>
@@ -96223,7 +96223,7 @@
         <v>42</v>
       </c>
       <c r="R60">
-        <v>0.1870333333333333</v>
+        <v>0.18703333333333336</v>
       </c>
       <c r="S60" t="s">
         <v>586</v>
@@ -96419,7 +96419,7 @@
         <v>46</v>
       </c>
       <c r="R74">
-        <v>0.24393333333333334</v>
+        <v>0.24393333333333336</v>
       </c>
       <c r="S74" t="s">
         <v>586</v>
@@ -96643,7 +96643,7 @@
         <v>46</v>
       </c>
       <c r="R90">
-        <v>0.25629999999999997</v>
+        <v>0.25630000000000003</v>
       </c>
       <c r="S90" t="s">
         <v>586</v>
@@ -96671,7 +96671,7 @@
         <v>42</v>
       </c>
       <c r="R92">
-        <v>0.20150000000000001</v>
+        <v>0.20149999999999998</v>
       </c>
       <c r="S92" t="s">
         <v>586</v>
@@ -96685,7 +96685,7 @@
         <v>44</v>
       </c>
       <c r="R93">
-        <v>0.26846666666666663</v>
+        <v>0.26846666666666669</v>
       </c>
       <c r="S93" t="s">
         <v>586</v>
@@ -96727,7 +96727,7 @@
         <v>42</v>
       </c>
       <c r="R96">
-        <v>0.20249999999999999</v>
+        <v>0.20250000000000001</v>
       </c>
       <c r="S96" t="s">
         <v>586</v>
@@ -96741,7 +96741,7 @@
         <v>44</v>
       </c>
       <c r="R97">
-        <v>0.32883333333333331</v>
+        <v>0.32883333333333337</v>
       </c>
       <c r="S97" t="s">
         <v>586</v>
@@ -96783,7 +96783,7 @@
         <v>42</v>
       </c>
       <c r="R100">
-        <v>0.22070000000000001</v>
+        <v>0.22069999999999998</v>
       </c>
       <c r="S100" t="s">
         <v>586</v>
@@ -96895,7 +96895,7 @@
         <v>42</v>
       </c>
       <c r="R108">
-        <v>0.2723666666666667</v>
+        <v>0.27236666666666665</v>
       </c>
       <c r="S108" t="s">
         <v>586</v>
@@ -96923,7 +96923,7 @@
         <v>46</v>
       </c>
       <c r="R110">
-        <v>0.2840333333333333</v>
+        <v>0.28403333333333336</v>
       </c>
       <c r="S110" t="s">
         <v>586</v>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DECBEC7C-FBA9-4B03-948A-743FAA59251A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83427FE1-8E29-4EA4-9239-DCFE853041B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1770,13 +1770,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S2aH2,S4aH2,S3aH2,S1aH2</t>
+    <t>S4aH2,S1aH2,S2aH2,S3aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S2aH3,S3aH3,S4aH1,S1aH1,S4aH3,S2aH1,S1aH3,S3aH1</t>
+    <t>S3aH1,S1aH1,S4aH3,S2aH1,S1aH3,S3aH3,S4aH1,S2aH3</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S2aH3,S3aH3,S4aH1,S1aH1,S4aH3,S2aH1,S1aH3,S3aH1</v>
+        <v>S3aH1,S1aH1,S4aH3,S2aH1,S1aH3,S3aH3,S4aH1,S2aH3</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S2aH2,S4aH2,S3aH2,S1aH2</v>
+        <v>S4aH2,S1aH2,S2aH2,S3aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -2501,7 +2501,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C521BD5-5645-41AC-B786-9D2F667C1233}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54352458-D966-499A-8110-638B9B1433D0}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2581,7 +2581,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCBF04FE-FB1E-4D68-957F-8AD60A91EAFA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65F4ABA8-B29B-4738-AA52-2195A0075143}">
   <dimension ref="B9:O1174"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -40395,7 +40395,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECBE9103-C4A1-47AB-AD44-27444228A19B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29D914A3-022D-4E24-88FC-76D3974058A9}">
   <dimension ref="B9:CI256"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -95064,7 +95064,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{256CD0A2-E34D-420F-8BFB-977C134115D2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A54E7A9F-693C-4BBC-9D8E-290BB19CB0B6}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -95291,7 +95291,7 @@
         <v>46</v>
       </c>
       <c r="R14">
-        <v>0.19036666666666668</v>
+        <v>0.19036666666666666</v>
       </c>
       <c r="S14" t="s">
         <v>586</v>
@@ -95639,7 +95639,7 @@
         <v>38</v>
       </c>
       <c r="R23">
-        <v>0.22023333333333336</v>
+        <v>0.22023333333333331</v>
       </c>
       <c r="S23" t="s">
         <v>586</v>
@@ -95699,7 +95699,7 @@
         <v>46</v>
       </c>
       <c r="R26">
-        <v>0.25126666666666664</v>
+        <v>0.25126666666666669</v>
       </c>
       <c r="S26" t="s">
         <v>586</v>
@@ -95779,7 +95779,7 @@
         <v>46</v>
       </c>
       <c r="R30">
-        <v>0.22429999999999997</v>
+        <v>0.22430000000000003</v>
       </c>
       <c r="S30" t="s">
         <v>586</v>
@@ -95799,7 +95799,7 @@
         <v>38</v>
       </c>
       <c r="R31">
-        <v>0.17966666666666664</v>
+        <v>0.17966666666666667</v>
       </c>
       <c r="S31" t="s">
         <v>586</v>
@@ -96097,7 +96097,7 @@
         <v>38</v>
       </c>
       <c r="R51">
-        <v>0.19266666666666665</v>
+        <v>0.19266666666666668</v>
       </c>
       <c r="S51" t="s">
         <v>586</v>
@@ -96139,7 +96139,7 @@
         <v>46</v>
       </c>
       <c r="R54">
-        <v>0.21993333333333334</v>
+        <v>0.21993333333333331</v>
       </c>
       <c r="S54" t="s">
         <v>586</v>
@@ -96153,7 +96153,7 @@
         <v>38</v>
       </c>
       <c r="R55">
-        <v>0.21196666666666666</v>
+        <v>0.21196666666666664</v>
       </c>
       <c r="S55" t="s">
         <v>586</v>
@@ -96195,7 +96195,7 @@
         <v>46</v>
       </c>
       <c r="R58">
-        <v>0.23783333333333331</v>
+        <v>0.23783333333333334</v>
       </c>
       <c r="S58" t="s">
         <v>586</v>
@@ -96419,7 +96419,7 @@
         <v>46</v>
       </c>
       <c r="R74">
-        <v>0.24393333333333336</v>
+        <v>0.24393333333333334</v>
       </c>
       <c r="S74" t="s">
         <v>586</v>
@@ -96643,7 +96643,7 @@
         <v>46</v>
       </c>
       <c r="R90">
-        <v>0.25630000000000003</v>
+        <v>0.25629999999999997</v>
       </c>
       <c r="S90" t="s">
         <v>586</v>
@@ -96769,7 +96769,7 @@
         <v>38</v>
       </c>
       <c r="R99">
-        <v>0.19093333333333332</v>
+        <v>0.19093333333333337</v>
       </c>
       <c r="S99" t="s">
         <v>586</v>
@@ -96923,7 +96923,7 @@
         <v>46</v>
       </c>
       <c r="R110">
-        <v>0.28403333333333336</v>
+        <v>0.2840333333333333</v>
       </c>
       <c r="S110" t="s">
         <v>586</v>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83427FE1-8E29-4EA4-9239-DCFE853041B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B7AA8E6-DFCC-43E1-837A-1799007831F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1770,13 +1770,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S4aH2,S1aH2,S2aH2,S3aH2</t>
+    <t>S1aH2,S4aH2,S2aH2,S3aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S3aH1,S1aH1,S4aH3,S2aH1,S1aH3,S3aH3,S4aH1,S2aH3</t>
+    <t>S1aH3,S3aH1,S2aH1,S3aH3,S4aH1,S1aH1,S4aH3,S2aH3</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S3aH1,S1aH1,S4aH3,S2aH1,S1aH3,S3aH3,S4aH1,S2aH3</v>
+        <v>S1aH3,S3aH1,S2aH1,S3aH3,S4aH1,S1aH1,S4aH3,S2aH3</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S4aH2,S1aH2,S2aH2,S3aH2</v>
+        <v>S1aH2,S4aH2,S2aH2,S3aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -2501,7 +2501,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54352458-D966-499A-8110-638B9B1433D0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17D3846A-0EB2-45B4-9A7C-E752EAC18680}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2581,7 +2581,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65F4ABA8-B29B-4738-AA52-2195A0075143}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D4AC251-5E00-4BCE-B0B1-B18FEF9B2407}">
   <dimension ref="B9:O1174"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -40395,7 +40395,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29D914A3-022D-4E24-88FC-76D3974058A9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06E3D75B-22A0-41C2-8686-93B43209F1E3}">
   <dimension ref="B9:CI256"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -95064,7 +95064,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A54E7A9F-693C-4BBC-9D8E-290BB19CB0B6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AA7B988-B44A-4BE8-8F18-4E9150EA733A}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -95537,7 +95537,7 @@
         <v>42</v>
       </c>
       <c r="R20">
-        <v>0.24216666666666672</v>
+        <v>0.24216666666666667</v>
       </c>
       <c r="S20" t="s">
         <v>586</v>
@@ -95779,7 +95779,7 @@
         <v>46</v>
       </c>
       <c r="R30">
-        <v>0.22430000000000003</v>
+        <v>0.22429999999999997</v>
       </c>
       <c r="S30" t="s">
         <v>586</v>
@@ -95915,7 +95915,7 @@
         <v>46</v>
       </c>
       <c r="R38">
-        <v>0.22670000000000001</v>
+        <v>0.22669999999999998</v>
       </c>
       <c r="S38" t="s">
         <v>586</v>
@@ -95943,7 +95943,7 @@
         <v>42</v>
       </c>
       <c r="R40">
-        <v>0.21413333333333337</v>
+        <v>0.21413333333333331</v>
       </c>
       <c r="S40" t="s">
         <v>586</v>
@@ -96055,7 +96055,7 @@
         <v>42</v>
       </c>
       <c r="R48">
-        <v>0.1966</v>
+        <v>0.19660000000000002</v>
       </c>
       <c r="S48" t="s">
         <v>586</v>
@@ -96279,7 +96279,7 @@
         <v>42</v>
       </c>
       <c r="R64">
-        <v>0.2127</v>
+        <v>0.21269999999999997</v>
       </c>
       <c r="S64" t="s">
         <v>586</v>
@@ -96447,7 +96447,7 @@
         <v>42</v>
       </c>
       <c r="R76">
-        <v>0.28030000000000005</v>
+        <v>0.28029999999999999</v>
       </c>
       <c r="S76" t="s">
         <v>586</v>
@@ -96643,7 +96643,7 @@
         <v>46</v>
       </c>
       <c r="R90">
-        <v>0.25629999999999997</v>
+        <v>0.25630000000000003</v>
       </c>
       <c r="S90" t="s">
         <v>586</v>
@@ -96671,7 +96671,7 @@
         <v>42</v>
       </c>
       <c r="R92">
-        <v>0.20149999999999998</v>
+        <v>0.20150000000000001</v>
       </c>
       <c r="S92" t="s">
         <v>586</v>
@@ -96727,7 +96727,7 @@
         <v>42</v>
       </c>
       <c r="R96">
-        <v>0.20250000000000001</v>
+        <v>0.20249999999999999</v>
       </c>
       <c r="S96" t="s">
         <v>586</v>
@@ -96923,7 +96923,7 @@
         <v>46</v>
       </c>
       <c r="R110">
-        <v>0.2840333333333333</v>
+        <v>0.28403333333333336</v>
       </c>
       <c r="S110" t="s">
         <v>586</v>
@@ -96979,7 +96979,7 @@
         <v>46</v>
       </c>
       <c r="R114">
-        <v>0.30119999999999997</v>
+        <v>0.30120000000000002</v>
       </c>
       <c r="S114" t="s">
         <v>586</v>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B7AA8E6-DFCC-43E1-837A-1799007831F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19019C89-1C8F-49D6-AE3A-8B68868CD9E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1770,13 +1770,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S1aH2,S4aH2,S2aH2,S3aH2</t>
+    <t>S1aH2,S2aH2,S3aH2,S4aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S1aH3,S3aH1,S2aH1,S3aH3,S4aH1,S1aH1,S4aH3,S2aH3</t>
+    <t>S2aH3,S1aH3,S3aH3,S4aH1,S3aH1,S2aH1,S1aH1,S4aH3</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S1aH3,S3aH1,S2aH1,S3aH3,S4aH1,S1aH1,S4aH3,S2aH3</v>
+        <v>S2aH3,S1aH3,S3aH3,S4aH1,S3aH1,S2aH1,S1aH1,S4aH3</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S1aH2,S4aH2,S2aH2,S3aH2</v>
+        <v>S1aH2,S2aH2,S3aH2,S4aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -2501,7 +2501,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17D3846A-0EB2-45B4-9A7C-E752EAC18680}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F36C206C-DCF3-40F1-8163-8F03FFD4836B}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2581,7 +2581,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D4AC251-5E00-4BCE-B0B1-B18FEF9B2407}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F87A120A-47DA-4AC1-8962-29B2F3837A4A}">
   <dimension ref="B9:O1174"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -40395,7 +40395,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06E3D75B-22A0-41C2-8686-93B43209F1E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18AD409D-1900-48F6-8F86-DC6EBCF56F87}">
   <dimension ref="B9:CI256"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -95064,7 +95064,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AA7B988-B44A-4BE8-8F18-4E9150EA733A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D5CD425-6717-451B-83B1-7C009CB7D1DB}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -95414,7 +95414,7 @@
         <v>44</v>
       </c>
       <c r="R17">
-        <v>0.27526666666666672</v>
+        <v>0.27526666666666666</v>
       </c>
       <c r="S17" t="s">
         <v>586</v>
@@ -95537,7 +95537,7 @@
         <v>42</v>
       </c>
       <c r="R20">
-        <v>0.24216666666666667</v>
+        <v>0.24216666666666672</v>
       </c>
       <c r="S20" t="s">
         <v>586</v>
@@ -95779,7 +95779,7 @@
         <v>46</v>
       </c>
       <c r="R30">
-        <v>0.22429999999999997</v>
+        <v>0.22430000000000003</v>
       </c>
       <c r="S30" t="s">
         <v>586</v>
@@ -95915,7 +95915,7 @@
         <v>46</v>
       </c>
       <c r="R38">
-        <v>0.22669999999999998</v>
+        <v>0.22670000000000001</v>
       </c>
       <c r="S38" t="s">
         <v>586</v>
@@ -95943,7 +95943,7 @@
         <v>42</v>
       </c>
       <c r="R40">
-        <v>0.21413333333333331</v>
+        <v>0.21413333333333337</v>
       </c>
       <c r="S40" t="s">
         <v>586</v>
@@ -96013,7 +96013,7 @@
         <v>44</v>
       </c>
       <c r="R45">
-        <v>0.29126666666666662</v>
+        <v>0.29126666666666667</v>
       </c>
       <c r="S45" t="s">
         <v>586</v>
@@ -96055,7 +96055,7 @@
         <v>42</v>
       </c>
       <c r="R48">
-        <v>0.19660000000000002</v>
+        <v>0.1966</v>
       </c>
       <c r="S48" t="s">
         <v>586</v>
@@ -96279,7 +96279,7 @@
         <v>42</v>
       </c>
       <c r="R64">
-        <v>0.21269999999999997</v>
+        <v>0.2127</v>
       </c>
       <c r="S64" t="s">
         <v>586</v>
@@ -96447,7 +96447,7 @@
         <v>42</v>
       </c>
       <c r="R76">
-        <v>0.28029999999999999</v>
+        <v>0.28030000000000005</v>
       </c>
       <c r="S76" t="s">
         <v>586</v>
@@ -96461,7 +96461,7 @@
         <v>44</v>
       </c>
       <c r="R77">
-        <v>0.32863333333333333</v>
+        <v>0.32863333333333339</v>
       </c>
       <c r="S77" t="s">
         <v>586</v>
@@ -96517,7 +96517,7 @@
         <v>44</v>
       </c>
       <c r="R81">
-        <v>0.26493333333333335</v>
+        <v>0.2649333333333333</v>
       </c>
       <c r="S81" t="s">
         <v>586</v>
@@ -96629,7 +96629,7 @@
         <v>44</v>
       </c>
       <c r="R89">
-        <v>0.31253333333333333</v>
+        <v>0.31253333333333339</v>
       </c>
       <c r="S89" t="s">
         <v>586</v>
@@ -96643,7 +96643,7 @@
         <v>46</v>
       </c>
       <c r="R90">
-        <v>0.25630000000000003</v>
+        <v>0.25629999999999997</v>
       </c>
       <c r="S90" t="s">
         <v>586</v>
@@ -96671,7 +96671,7 @@
         <v>42</v>
       </c>
       <c r="R92">
-        <v>0.20150000000000001</v>
+        <v>0.20149999999999998</v>
       </c>
       <c r="S92" t="s">
         <v>586</v>
@@ -96685,7 +96685,7 @@
         <v>44</v>
       </c>
       <c r="R93">
-        <v>0.26846666666666669</v>
+        <v>0.26846666666666663</v>
       </c>
       <c r="S93" t="s">
         <v>586</v>
@@ -96727,7 +96727,7 @@
         <v>42</v>
       </c>
       <c r="R96">
-        <v>0.20249999999999999</v>
+        <v>0.20250000000000001</v>
       </c>
       <c r="S96" t="s">
         <v>586</v>
@@ -96741,7 +96741,7 @@
         <v>44</v>
       </c>
       <c r="R97">
-        <v>0.32883333333333337</v>
+        <v>0.32883333333333331</v>
       </c>
       <c r="S97" t="s">
         <v>586</v>
@@ -96923,7 +96923,7 @@
         <v>46</v>
       </c>
       <c r="R110">
-        <v>0.28403333333333336</v>
+        <v>0.2840333333333333</v>
       </c>
       <c r="S110" t="s">
         <v>586</v>
@@ -96965,7 +96965,7 @@
         <v>44</v>
       </c>
       <c r="R113">
-        <v>0.32246666666666668</v>
+        <v>0.32246666666666662</v>
       </c>
       <c r="S113" t="s">
         <v>586</v>
@@ -96979,7 +96979,7 @@
         <v>46</v>
       </c>
       <c r="R114">
-        <v>0.30120000000000002</v>
+        <v>0.30119999999999997</v>
       </c>
       <c r="S114" t="s">
         <v>586</v>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19019C89-1C8F-49D6-AE3A-8B68868CD9E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C73B20F7-2085-4828-A606-97AFB68C0AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1770,13 +1770,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S1aH2,S2aH2,S3aH2,S4aH2</t>
+    <t>S4aH2,S1aH2,S3aH2,S2aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S2aH3,S1aH3,S3aH3,S4aH1,S3aH1,S2aH1,S1aH1,S4aH3</t>
+    <t>S2aH1,S2aH3,S1aH3,S3aH3,S4aH1,S1aH1,S4aH3,S3aH1</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S2aH3,S1aH3,S3aH3,S4aH1,S3aH1,S2aH1,S1aH1,S4aH3</v>
+        <v>S2aH1,S2aH3,S1aH3,S3aH3,S4aH1,S1aH1,S4aH3,S3aH1</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S1aH2,S2aH2,S3aH2,S4aH2</v>
+        <v>S4aH2,S1aH2,S3aH2,S2aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -2501,7 +2501,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F36C206C-DCF3-40F1-8163-8F03FFD4836B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81DCFE0C-E335-47B7-A71C-A4497FF1A385}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2581,7 +2581,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F87A120A-47DA-4AC1-8962-29B2F3837A4A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A22819A0-3B4A-4A14-A72D-A350569043F1}">
   <dimension ref="B9:O1174"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -40395,7 +40395,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18AD409D-1900-48F6-8F86-DC6EBCF56F87}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2132DE50-44E9-41EE-A83B-CE9D9EADC530}">
   <dimension ref="B9:CI256"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -95064,7 +95064,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D5CD425-6717-451B-83B1-7C009CB7D1DB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AEE3262-E4C8-4425-A4A5-912561553079}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -95332,7 +95332,7 @@
         <v>38</v>
       </c>
       <c r="R15">
-        <v>0.18506666666666668</v>
+        <v>0.18506666666666663</v>
       </c>
       <c r="S15" t="s">
         <v>586</v>
@@ -95537,7 +95537,7 @@
         <v>42</v>
       </c>
       <c r="R20">
-        <v>0.24216666666666672</v>
+        <v>0.24216666666666667</v>
       </c>
       <c r="S20" t="s">
         <v>586</v>
@@ -95639,7 +95639,7 @@
         <v>38</v>
       </c>
       <c r="R23">
-        <v>0.22023333333333331</v>
+        <v>0.22023333333333336</v>
       </c>
       <c r="S23" t="s">
         <v>586</v>
@@ -95719,7 +95719,7 @@
         <v>38</v>
       </c>
       <c r="R27">
-        <v>0.18723333333333336</v>
+        <v>0.18723333333333333</v>
       </c>
       <c r="S27" t="s">
         <v>586</v>
@@ -95779,7 +95779,7 @@
         <v>46</v>
       </c>
       <c r="R30">
-        <v>0.22430000000000003</v>
+        <v>0.22429999999999997</v>
       </c>
       <c r="S30" t="s">
         <v>586</v>
@@ -95799,7 +95799,7 @@
         <v>38</v>
       </c>
       <c r="R31">
-        <v>0.17966666666666667</v>
+        <v>0.17966666666666664</v>
       </c>
       <c r="S31" t="s">
         <v>586</v>
@@ -95915,7 +95915,7 @@
         <v>46</v>
       </c>
       <c r="R38">
-        <v>0.22670000000000001</v>
+        <v>0.22669999999999998</v>
       </c>
       <c r="S38" t="s">
         <v>586</v>
@@ -95943,7 +95943,7 @@
         <v>42</v>
       </c>
       <c r="R40">
-        <v>0.21413333333333337</v>
+        <v>0.21413333333333331</v>
       </c>
       <c r="S40" t="s">
         <v>586</v>
@@ -95985,7 +95985,7 @@
         <v>38</v>
       </c>
       <c r="R43">
-        <v>0.20276666666666665</v>
+        <v>0.20276666666666668</v>
       </c>
       <c r="S43" t="s">
         <v>586</v>
@@ -96055,7 +96055,7 @@
         <v>42</v>
       </c>
       <c r="R48">
-        <v>0.1966</v>
+        <v>0.19660000000000002</v>
       </c>
       <c r="S48" t="s">
         <v>586</v>
@@ -96153,7 +96153,7 @@
         <v>38</v>
       </c>
       <c r="R55">
-        <v>0.21196666666666664</v>
+        <v>0.21196666666666666</v>
       </c>
       <c r="S55" t="s">
         <v>586</v>
@@ -96279,7 +96279,7 @@
         <v>42</v>
       </c>
       <c r="R64">
-        <v>0.2127</v>
+        <v>0.21269999999999997</v>
       </c>
       <c r="S64" t="s">
         <v>586</v>
@@ -96377,7 +96377,7 @@
         <v>38</v>
       </c>
       <c r="R71">
-        <v>0.20263333333333333</v>
+        <v>0.20263333333333336</v>
       </c>
       <c r="S71" t="s">
         <v>586</v>
@@ -96447,7 +96447,7 @@
         <v>42</v>
       </c>
       <c r="R76">
-        <v>0.28030000000000005</v>
+        <v>0.28029999999999999</v>
       </c>
       <c r="S76" t="s">
         <v>586</v>
@@ -96545,7 +96545,7 @@
         <v>38</v>
       </c>
       <c r="R83">
-        <v>0.18456666666666668</v>
+        <v>0.18456666666666666</v>
       </c>
       <c r="S83" t="s">
         <v>586</v>
@@ -96643,7 +96643,7 @@
         <v>46</v>
       </c>
       <c r="R90">
-        <v>0.25629999999999997</v>
+        <v>0.25630000000000003</v>
       </c>
       <c r="S90" t="s">
         <v>586</v>
@@ -96657,7 +96657,7 @@
         <v>38</v>
       </c>
       <c r="R91">
-        <v>0.23163333333333333</v>
+        <v>0.23163333333333336</v>
       </c>
       <c r="S91" t="s">
         <v>586</v>
@@ -96671,7 +96671,7 @@
         <v>42</v>
       </c>
       <c r="R92">
-        <v>0.20149999999999998</v>
+        <v>0.20150000000000001</v>
       </c>
       <c r="S92" t="s">
         <v>586</v>
@@ -96727,7 +96727,7 @@
         <v>42</v>
       </c>
       <c r="R96">
-        <v>0.20250000000000001</v>
+        <v>0.20249999999999999</v>
       </c>
       <c r="S96" t="s">
         <v>586</v>
@@ -96881,7 +96881,7 @@
         <v>38</v>
       </c>
       <c r="R107">
-        <v>0.17253333333333334</v>
+        <v>0.17253333333333332</v>
       </c>
       <c r="S107" t="s">
         <v>586</v>
@@ -96923,7 +96923,7 @@
         <v>46</v>
       </c>
       <c r="R110">
-        <v>0.2840333333333333</v>
+        <v>0.28403333333333336</v>
       </c>
       <c r="S110" t="s">
         <v>586</v>
@@ -96979,7 +96979,7 @@
         <v>46</v>
       </c>
       <c r="R114">
-        <v>0.30119999999999997</v>
+        <v>0.30120000000000002</v>
       </c>
       <c r="S114" t="s">
         <v>586</v>
@@ -97049,7 +97049,7 @@
         <v>38</v>
       </c>
       <c r="R119">
-        <v>0.23606666666666665</v>
+        <v>0.23606666666666667</v>
       </c>
       <c r="S119" t="s">
         <v>586</v>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C73B20F7-2085-4828-A606-97AFB68C0AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92BA43F8-0E42-4CCD-8507-D3BDED9F2092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1770,13 +1770,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S4aH2,S1aH2,S3aH2,S2aH2</t>
+    <t>S2aH2,S3aH2,S4aH2,S1aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S2aH1,S2aH3,S1aH3,S3aH3,S4aH1,S1aH1,S4aH3,S3aH1</t>
+    <t>S3aH3,S4aH1,S1aH1,S4aH3,S2aH3,S3aH1,S2aH1,S1aH3</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S2aH1,S2aH3,S1aH3,S3aH3,S4aH1,S1aH1,S4aH3,S3aH1</v>
+        <v>S3aH3,S4aH1,S1aH1,S4aH3,S2aH3,S3aH1,S2aH1,S1aH3</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S4aH2,S1aH2,S3aH2,S2aH2</v>
+        <v>S2aH2,S3aH2,S4aH2,S1aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -2501,7 +2501,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81DCFE0C-E335-47B7-A71C-A4497FF1A385}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AD89765-CA36-4FE6-96EA-1DEF17125F4D}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2581,7 +2581,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A22819A0-3B4A-4A14-A72D-A350569043F1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57555E67-E506-4BCF-A7FA-052DB9131731}">
   <dimension ref="B9:O1174"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -40395,7 +40395,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2132DE50-44E9-41EE-A83B-CE9D9EADC530}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6491D8B3-FEAE-420A-8D20-B1263470E459}">
   <dimension ref="B9:CI256"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -95064,7 +95064,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AEE3262-E4C8-4425-A4A5-912561553079}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F384D8B-5898-4BB6-BBE0-C8D573A97368}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -95414,7 +95414,7 @@
         <v>44</v>
       </c>
       <c r="R17">
-        <v>0.27526666666666666</v>
+        <v>0.27526666666666672</v>
       </c>
       <c r="S17" t="s">
         <v>586</v>
@@ -95537,7 +95537,7 @@
         <v>42</v>
       </c>
       <c r="R20">
-        <v>0.24216666666666667</v>
+        <v>0.24216666666666664</v>
       </c>
       <c r="S20" t="s">
         <v>586</v>
@@ -95779,7 +95779,7 @@
         <v>46</v>
       </c>
       <c r="R30">
-        <v>0.22429999999999997</v>
+        <v>0.22430000000000003</v>
       </c>
       <c r="S30" t="s">
         <v>586</v>
@@ -95887,7 +95887,7 @@
         <v>42</v>
       </c>
       <c r="R36">
-        <v>0.19306666666666669</v>
+        <v>0.19306666666666664</v>
       </c>
       <c r="S36" t="s">
         <v>586</v>
@@ -95915,7 +95915,7 @@
         <v>46</v>
       </c>
       <c r="R38">
-        <v>0.22669999999999998</v>
+        <v>0.22670000000000001</v>
       </c>
       <c r="S38" t="s">
         <v>586</v>
@@ -95943,7 +95943,7 @@
         <v>42</v>
       </c>
       <c r="R40">
-        <v>0.21413333333333331</v>
+        <v>0.21413333333333337</v>
       </c>
       <c r="S40" t="s">
         <v>586</v>
@@ -96013,7 +96013,7 @@
         <v>44</v>
       </c>
       <c r="R45">
-        <v>0.29126666666666667</v>
+        <v>0.29126666666666662</v>
       </c>
       <c r="S45" t="s">
         <v>586</v>
@@ -96055,7 +96055,7 @@
         <v>42</v>
       </c>
       <c r="R48">
-        <v>0.19660000000000002</v>
+        <v>0.1966</v>
       </c>
       <c r="S48" t="s">
         <v>586</v>
@@ -96223,7 +96223,7 @@
         <v>42</v>
       </c>
       <c r="R60">
-        <v>0.18703333333333336</v>
+        <v>0.1870333333333333</v>
       </c>
       <c r="S60" t="s">
         <v>586</v>
@@ -96279,7 +96279,7 @@
         <v>42</v>
       </c>
       <c r="R64">
-        <v>0.21269999999999997</v>
+        <v>0.2127</v>
       </c>
       <c r="S64" t="s">
         <v>586</v>
@@ -96447,7 +96447,7 @@
         <v>42</v>
       </c>
       <c r="R76">
-        <v>0.28029999999999999</v>
+        <v>0.28030000000000005</v>
       </c>
       <c r="S76" t="s">
         <v>586</v>
@@ -96461,7 +96461,7 @@
         <v>44</v>
       </c>
       <c r="R77">
-        <v>0.32863333333333339</v>
+        <v>0.32863333333333333</v>
       </c>
       <c r="S77" t="s">
         <v>586</v>
@@ -96517,7 +96517,7 @@
         <v>44</v>
       </c>
       <c r="R81">
-        <v>0.2649333333333333</v>
+        <v>0.26493333333333335</v>
       </c>
       <c r="S81" t="s">
         <v>586</v>
@@ -96629,7 +96629,7 @@
         <v>44</v>
       </c>
       <c r="R89">
-        <v>0.31253333333333339</v>
+        <v>0.31253333333333333</v>
       </c>
       <c r="S89" t="s">
         <v>586</v>
@@ -96643,7 +96643,7 @@
         <v>46</v>
       </c>
       <c r="R90">
-        <v>0.25630000000000003</v>
+        <v>0.25629999999999997</v>
       </c>
       <c r="S90" t="s">
         <v>586</v>
@@ -96783,7 +96783,7 @@
         <v>42</v>
       </c>
       <c r="R100">
-        <v>0.22069999999999998</v>
+        <v>0.22070000000000001</v>
       </c>
       <c r="S100" t="s">
         <v>586</v>
@@ -96895,7 +96895,7 @@
         <v>42</v>
       </c>
       <c r="R108">
-        <v>0.27236666666666665</v>
+        <v>0.2723666666666667</v>
       </c>
       <c r="S108" t="s">
         <v>586</v>
@@ -96923,7 +96923,7 @@
         <v>46</v>
       </c>
       <c r="R110">
-        <v>0.28403333333333336</v>
+        <v>0.2840333333333333</v>
       </c>
       <c r="S110" t="s">
         <v>586</v>
@@ -96965,7 +96965,7 @@
         <v>44</v>
       </c>
       <c r="R113">
-        <v>0.32246666666666662</v>
+        <v>0.32246666666666668</v>
       </c>
       <c r="S113" t="s">
         <v>586</v>
@@ -96979,7 +96979,7 @@
         <v>46</v>
       </c>
       <c r="R114">
-        <v>0.30120000000000002</v>
+        <v>0.30119999999999997</v>
       </c>
       <c r="S114" t="s">
         <v>586</v>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92BA43F8-0E42-4CCD-8507-D3BDED9F2092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{465AC730-FB10-4967-A741-78A2978854D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1770,13 +1770,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S2aH2,S3aH2,S4aH2,S1aH2</t>
+    <t>S4aH2,S3aH2,S1aH2,S2aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S3aH3,S4aH1,S1aH1,S4aH3,S2aH3,S3aH1,S2aH1,S1aH3</t>
+    <t>S2aH1,S1aH1,S4aH3,S3aH1,S2aH3,S1aH3,S3aH3,S4aH1</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S3aH3,S4aH1,S1aH1,S4aH3,S2aH3,S3aH1,S2aH1,S1aH3</v>
+        <v>S2aH1,S1aH1,S4aH3,S3aH1,S2aH3,S1aH3,S3aH3,S4aH1</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S2aH2,S3aH2,S4aH2,S1aH2</v>
+        <v>S4aH2,S3aH2,S1aH2,S2aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -2501,7 +2501,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AD89765-CA36-4FE6-96EA-1DEF17125F4D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9CF04E8-9594-4655-B8C0-CFA86B213403}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2581,7 +2581,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57555E67-E506-4BCF-A7FA-052DB9131731}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51BC3351-82DA-4CA1-9839-A9F96DA098A3}">
   <dimension ref="B9:O1174"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -40395,7 +40395,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6491D8B3-FEAE-420A-8D20-B1263470E459}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{427B442A-B8C5-4B18-AF9B-37CD0992C390}">
   <dimension ref="B9:CI256"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -95064,7 +95064,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F384D8B-5898-4BB6-BBE0-C8D573A97368}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B324C84-FCEA-4907-9468-4653D6E54A3E}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -95332,7 +95332,7 @@
         <v>38</v>
       </c>
       <c r="R15">
-        <v>0.18506666666666663</v>
+        <v>0.18506666666666668</v>
       </c>
       <c r="S15" t="s">
         <v>586</v>
@@ -95719,7 +95719,7 @@
         <v>38</v>
       </c>
       <c r="R27">
-        <v>0.18723333333333333</v>
+        <v>0.18723333333333336</v>
       </c>
       <c r="S27" t="s">
         <v>586</v>
@@ -95985,7 +95985,7 @@
         <v>38</v>
       </c>
       <c r="R43">
-        <v>0.20276666666666668</v>
+        <v>0.20276666666666665</v>
       </c>
       <c r="S43" t="s">
         <v>586</v>
@@ -96097,7 +96097,7 @@
         <v>38</v>
       </c>
       <c r="R51">
-        <v>0.19266666666666668</v>
+        <v>0.19266666666666665</v>
       </c>
       <c r="S51" t="s">
         <v>586</v>
@@ -96377,7 +96377,7 @@
         <v>38</v>
       </c>
       <c r="R71">
-        <v>0.20263333333333336</v>
+        <v>0.20263333333333333</v>
       </c>
       <c r="S71" t="s">
         <v>586</v>
@@ -96545,7 +96545,7 @@
         <v>38</v>
       </c>
       <c r="R83">
-        <v>0.18456666666666666</v>
+        <v>0.18456666666666668</v>
       </c>
       <c r="S83" t="s">
         <v>586</v>
@@ -96657,7 +96657,7 @@
         <v>38</v>
       </c>
       <c r="R91">
-        <v>0.23163333333333336</v>
+        <v>0.23163333333333333</v>
       </c>
       <c r="S91" t="s">
         <v>586</v>
@@ -96769,7 +96769,7 @@
         <v>38</v>
       </c>
       <c r="R99">
-        <v>0.19093333333333337</v>
+        <v>0.19093333333333332</v>
       </c>
       <c r="S99" t="s">
         <v>586</v>
@@ -96881,7 +96881,7 @@
         <v>38</v>
       </c>
       <c r="R107">
-        <v>0.17253333333333332</v>
+        <v>0.17253333333333334</v>
       </c>
       <c r="S107" t="s">
         <v>586</v>
@@ -97049,7 +97049,7 @@
         <v>38</v>
       </c>
       <c r="R119">
-        <v>0.23606666666666667</v>
+        <v>0.23606666666666665</v>
       </c>
       <c r="S119" t="s">
         <v>586</v>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DFC9D5F-BE1C-489F-B646-D9A66E0C3D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C637E93C-7262-4C8E-BE52-AFCD4191D440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1770,13 +1770,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S4aH2,S1aH2,S3aH2,S2aH2</t>
+    <t>S2aH2,S3aH2,S4aH2,S1aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S2aH1,S2aH3,S1aH3,S1aH1,S4aH3,S3aH3,S4aH1,S3aH1</t>
+    <t>S3aH3,S4aH1,S2aH3,S3aH1,S1aH1,S4aH3,S2aH1,S1aH3</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S2aH1,S2aH3,S1aH3,S1aH1,S4aH3,S3aH3,S4aH1,S3aH1</v>
+        <v>S3aH3,S4aH1,S2aH3,S3aH1,S1aH1,S4aH3,S2aH1,S1aH3</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S4aH2,S1aH2,S3aH2,S2aH2</v>
+        <v>S2aH2,S3aH2,S4aH2,S1aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -2501,7 +2501,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC5118AA-8F8F-4D96-8883-937A9B2F675B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4AFC51C-2A46-42E0-AC69-937C2DADE385}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2581,7 +2581,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDBB8AFD-E505-4B91-A3DB-EE841F694D94}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91BF8C5A-23AF-41B6-A1F5-996CA5DC8A69}">
   <dimension ref="B9:O1174"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3581,7 +3581,7 @@
         <v>53</v>
       </c>
       <c r="N35">
-        <v>7.4991086873863147E-2</v>
+        <v>6.8775547409385282E-2</v>
       </c>
       <c r="O35" t="s">
         <v>54</v>
@@ -3619,7 +3619,7 @@
         <v>55</v>
       </c>
       <c r="N36">
-        <v>9.5362040803134263E-2</v>
+        <v>9.2084614570064449E-2</v>
       </c>
       <c r="O36" t="s">
         <v>54</v>
@@ -3657,7 +3657,7 @@
         <v>56</v>
       </c>
       <c r="N37">
-        <v>6.2612113041063303E-2</v>
+        <v>5.1484562290557687E-2</v>
       </c>
       <c r="O37" t="s">
         <v>54</v>
@@ -3695,7 +3695,7 @@
         <v>57</v>
       </c>
       <c r="N38">
-        <v>7.1494296931245635E-2</v>
+        <v>7.7933327815050454E-2</v>
       </c>
       <c r="O38" t="s">
         <v>54</v>
@@ -3733,7 +3733,7 @@
         <v>58</v>
       </c>
       <c r="N39">
-        <v>8.501043249470952E-2</v>
+        <v>9.3964046028775547E-2</v>
       </c>
       <c r="O39" t="s">
         <v>54</v>
@@ -3771,7 +3771,7 @@
         <v>59</v>
       </c>
       <c r="N40">
-        <v>5.4686684720262654E-2</v>
+        <v>5.6459073611710306E-2</v>
       </c>
       <c r="O40" t="s">
         <v>54</v>
@@ -3809,7 +3809,7 @@
         <v>60</v>
       </c>
       <c r="N41">
-        <v>9.1514246410615105E-2</v>
+        <v>9.3867718944000991E-2</v>
       </c>
       <c r="O41" t="s">
         <v>54</v>
@@ -3847,7 +3847,7 @@
         <v>61</v>
       </c>
       <c r="N42">
-        <v>0.11409923991771696</v>
+        <v>0.12021442718550879</v>
       </c>
       <c r="O42" t="s">
         <v>54</v>
@@ -3885,7 +3885,7 @@
         <v>62</v>
       </c>
       <c r="N43">
-        <v>7.0040197448616573E-2</v>
+        <v>6.9444008342367955E-2</v>
       </c>
       <c r="O43" t="s">
         <v>54</v>
@@ -3923,7 +3923,7 @@
         <v>63</v>
       </c>
       <c r="N44">
-        <v>9.2925716497377991E-2</v>
+        <v>9.1228705150315489E-2</v>
       </c>
       <c r="O44" t="s">
         <v>54</v>
@@ -3961,7 +3961,7 @@
         <v>64</v>
       </c>
       <c r="N45">
-        <v>0.11492195034424738</v>
+        <v>0.11569066641066536</v>
       </c>
       <c r="O45" t="s">
         <v>54</v>
@@ -3999,7 +3999,7 @@
         <v>65</v>
       </c>
       <c r="N46">
-        <v>7.2341994517143418E-2</v>
+        <v>6.8853302241596887E-2</v>
       </c>
       <c r="O46" t="s">
         <v>54</v>
@@ -4013,7 +4013,7 @@
         <v>53</v>
       </c>
       <c r="D47">
-        <v>4.9725121247423676E-3</v>
+        <v>4.9718563198986598E-3</v>
       </c>
       <c r="E47" t="s">
         <v>54</v>
@@ -4025,7 +4025,7 @@
         <v>53</v>
       </c>
       <c r="I47">
-        <v>6.9050687864729135E-2</v>
+        <v>6.8940230526777224E-2</v>
       </c>
       <c r="J47" t="s">
         <v>54</v>
@@ -4037,7 +4037,7 @@
         <v>53</v>
       </c>
       <c r="N47">
-        <v>7.2234538822037883E-2</v>
+        <v>7.4193618300700939E-2</v>
       </c>
       <c r="O47" t="s">
         <v>54</v>
@@ -4051,7 +4051,7 @@
         <v>55</v>
       </c>
       <c r="D48">
-        <v>0.31861880886884825</v>
+        <v>0.31867500572756385</v>
       </c>
       <c r="E48" t="s">
         <v>54</v>
@@ -4063,7 +4063,7 @@
         <v>55</v>
       </c>
       <c r="I48">
-        <v>0.10244439223294692</v>
+        <v>0.10239008090983351</v>
       </c>
       <c r="J48" t="s">
         <v>54</v>
@@ -4075,7 +4075,7 @@
         <v>55</v>
       </c>
       <c r="N48">
-        <v>9.5174325239419086E-2</v>
+        <v>9.5689145391386135E-2</v>
       </c>
       <c r="O48" t="s">
         <v>54</v>
@@ -4089,7 +4089,7 @@
         <v>56</v>
       </c>
       <c r="D49">
-        <v>1.4631324968044663E-2</v>
+        <v>1.4637105611287669E-2</v>
       </c>
       <c r="E49" t="s">
         <v>54</v>
@@ -4101,7 +4101,7 @@
         <v>56</v>
       </c>
       <c r="I49">
-        <v>5.6062402049655936E-2</v>
+        <v>5.5951952056502954E-2</v>
       </c>
       <c r="J49" t="s">
         <v>54</v>
@@ -4113,7 +4113,7 @@
         <v>56</v>
       </c>
       <c r="N49">
-        <v>5.6343104615524837E-2</v>
+        <v>6.0906212260132445E-2</v>
       </c>
       <c r="O49" t="s">
         <v>54</v>
@@ -4127,7 +4127,7 @@
         <v>57</v>
       </c>
       <c r="D50">
-        <v>1.5587566281624732E-4</v>
+        <v>1.5577646557990958E-4</v>
       </c>
       <c r="E50" t="s">
         <v>54</v>
@@ -4139,7 +4139,7 @@
         <v>57</v>
       </c>
       <c r="I50">
-        <v>7.1572817286188736E-2</v>
+        <v>7.1564641087184605E-2</v>
       </c>
       <c r="J50" t="s">
         <v>54</v>
@@ -4151,7 +4151,7 @@
         <v>57</v>
       </c>
       <c r="N50">
-        <v>7.6364083552895631E-2</v>
+        <v>7.3168178827506397E-2</v>
       </c>
       <c r="O50" t="s">
         <v>54</v>
@@ -4165,7 +4165,7 @@
         <v>58</v>
       </c>
       <c r="D51">
-        <v>0.22605490559703517</v>
+        <v>0.22605910838790638</v>
       </c>
       <c r="E51" t="s">
         <v>54</v>
@@ -4177,7 +4177,7 @@
         <v>58</v>
       </c>
       <c r="I51">
-        <v>9.2121404949598071E-2</v>
+        <v>9.2158995947721228E-2</v>
       </c>
       <c r="J51" t="s">
         <v>54</v>
@@ -4189,7 +4189,7 @@
         <v>58</v>
       </c>
       <c r="N51">
-        <v>9.1321614188653505E-2</v>
+        <v>8.712308916920658E-2</v>
       </c>
       <c r="O51" t="s">
         <v>54</v>
@@ -4203,7 +4203,7 @@
         <v>59</v>
       </c>
       <c r="D52">
-        <v>2.9399454341921213E-3</v>
+        <v>2.9405396863189759E-3</v>
       </c>
       <c r="E52" t="s">
         <v>54</v>
@@ -4215,7 +4215,7 @@
         <v>59</v>
       </c>
       <c r="I52">
-        <v>5.2839457045197963E-2</v>
+        <v>5.28219545906147E-2</v>
       </c>
       <c r="J52" t="s">
         <v>54</v>
@@ -4227,7 +4227,7 @@
         <v>59</v>
       </c>
       <c r="N52">
-        <v>5.6256617536295773E-2</v>
+        <v>5.5382891506677884E-2</v>
       </c>
       <c r="O52" t="s">
         <v>54</v>
@@ -4253,7 +4253,7 @@
         <v>60</v>
       </c>
       <c r="I53">
-        <v>8.8153293951404033E-2</v>
+        <v>8.8218534189787201E-2</v>
       </c>
       <c r="J53" t="s">
         <v>54</v>
@@ -4265,7 +4265,7 @@
         <v>60</v>
       </c>
       <c r="N53">
-        <v>8.9303158344158945E-2</v>
+        <v>9.0045517539332445E-2</v>
       </c>
       <c r="O53" t="s">
         <v>54</v>
@@ -4279,7 +4279,7 @@
         <v>61</v>
       </c>
       <c r="D54">
-        <v>0.15377874861006402</v>
+        <v>0.15371197275191609</v>
       </c>
       <c r="E54" t="s">
         <v>54</v>
@@ -4291,7 +4291,7 @@
         <v>61</v>
       </c>
       <c r="I54">
-        <v>0.11355132710504627</v>
+        <v>0.11367979038102335</v>
       </c>
       <c r="J54" t="s">
         <v>54</v>
@@ -4303,7 +4303,7 @@
         <v>61</v>
       </c>
       <c r="N54">
-        <v>0.11454327926622597</v>
+        <v>0.11349701211953946</v>
       </c>
       <c r="O54" t="s">
         <v>54</v>
@@ -4317,7 +4317,7 @@
         <v>62</v>
       </c>
       <c r="D55">
-        <v>2.3632709197081228E-4</v>
+        <v>2.360339603456657E-4</v>
       </c>
       <c r="E55" t="s">
         <v>54</v>
@@ -4329,7 +4329,7 @@
         <v>62</v>
       </c>
       <c r="I55">
-        <v>6.6542989985189191E-2</v>
+        <v>6.6560763448342844E-2</v>
       </c>
       <c r="J55" t="s">
         <v>54</v>
@@ -4341,7 +4341,7 @@
         <v>62</v>
       </c>
       <c r="N55">
-        <v>6.7410315032824575E-2</v>
+        <v>6.8770103909677388E-2</v>
       </c>
       <c r="O55" t="s">
         <v>54</v>
@@ -4355,7 +4355,7 @@
         <v>63</v>
       </c>
       <c r="D56">
-        <v>4.2196813087844853E-3</v>
+        <v>4.2190031135610649E-3</v>
       </c>
       <c r="E56" t="s">
         <v>54</v>
@@ -4367,7 +4367,7 @@
         <v>63</v>
       </c>
       <c r="I56">
-        <v>9.2424198415708814E-2</v>
+        <v>9.2411271970524025E-2</v>
       </c>
       <c r="J56" t="s">
         <v>54</v>
@@ -4379,7 +4379,7 @@
         <v>63</v>
       </c>
       <c r="N56">
-        <v>9.4042358268070253E-2</v>
+        <v>9.3799606305061137E-2</v>
       </c>
       <c r="O56" t="s">
         <v>54</v>
@@ -4393,7 +4393,7 @@
         <v>64</v>
       </c>
       <c r="D57">
-        <v>0.26880816242679134</v>
+        <v>0.26880983057546903</v>
       </c>
       <c r="E57" t="s">
         <v>54</v>
@@ -4405,7 +4405,7 @@
         <v>64</v>
       </c>
       <c r="I57">
-        <v>0.1248830590047928</v>
+        <v>0.1249363088929502</v>
       </c>
       <c r="J57" t="s">
         <v>54</v>
@@ -4417,7 +4417,7 @@
         <v>64</v>
       </c>
       <c r="N57">
-        <v>0.1171265699472672</v>
+        <v>0.11590260777328143</v>
       </c>
       <c r="O57" t="s">
         <v>54</v>
@@ -4431,7 +4431,7 @@
         <v>65</v>
       </c>
       <c r="D58">
-        <v>5.5837079067126297E-3</v>
+        <v>5.5837674001525377E-3</v>
       </c>
       <c r="E58" t="s">
         <v>54</v>
@@ -4443,7 +4443,7 @@
         <v>65</v>
       </c>
       <c r="I58">
-        <v>7.0353970109538574E-2</v>
+        <v>7.036547599873838E-2</v>
       </c>
       <c r="J58" t="s">
         <v>54</v>
@@ -4455,7 +4455,7 @@
         <v>65</v>
       </c>
       <c r="N58">
-        <v>6.9880035186628567E-2</v>
+        <v>7.1522016897491755E-2</v>
       </c>
       <c r="O58" t="s">
         <v>54</v>
@@ -11333,7 +11333,7 @@
         <v>53</v>
       </c>
       <c r="N239">
-        <v>7.2048362061109109E-2</v>
+        <v>7.2582738190858503E-2</v>
       </c>
       <c r="O239" t="s">
         <v>54</v>
@@ -11371,7 +11371,7 @@
         <v>55</v>
       </c>
       <c r="N240">
-        <v>9.5739189596540639E-2</v>
+        <v>9.5822614213939353E-2</v>
       </c>
       <c r="O240" t="s">
         <v>54</v>
@@ -11409,7 +11409,7 @@
         <v>56</v>
       </c>
       <c r="N241">
-        <v>5.8321806588088221E-2</v>
+        <v>5.8587394389889601E-2</v>
       </c>
       <c r="O241" t="s">
         <v>54</v>
@@ -11447,7 +11447,7 @@
         <v>57</v>
       </c>
       <c r="N242">
-        <v>7.4055108632609251E-2</v>
+        <v>7.3795788076503721E-2</v>
       </c>
       <c r="O242" t="s">
         <v>54</v>
@@ -11485,7 +11485,7 @@
         <v>58</v>
       </c>
       <c r="N243">
-        <v>9.0398077045334271E-2</v>
+        <v>9.0130217588520273E-2</v>
       </c>
       <c r="O243" t="s">
         <v>54</v>
@@ -11523,7 +11523,7 @@
         <v>59</v>
       </c>
       <c r="N244">
-        <v>5.7214423466834863E-2</v>
+        <v>5.6834669875892245E-2</v>
       </c>
       <c r="O244" t="s">
         <v>54</v>
@@ -11561,7 +11561,7 @@
         <v>60</v>
       </c>
       <c r="N245">
-        <v>9.222382574827942E-2</v>
+        <v>9.2476291215822778E-2</v>
       </c>
       <c r="O245" t="s">
         <v>54</v>
@@ -11599,7 +11599,7 @@
         <v>61</v>
       </c>
       <c r="N246">
-        <v>0.11487066242169575</v>
+        <v>0.11529782750447927</v>
       </c>
       <c r="O246" t="s">
         <v>54</v>
@@ -11637,7 +11637,7 @@
         <v>62</v>
       </c>
       <c r="N247">
-        <v>6.8179384228084686E-2</v>
+        <v>6.8209213280889608E-2</v>
       </c>
       <c r="O247" t="s">
         <v>54</v>
@@ -11675,7 +11675,7 @@
         <v>63</v>
       </c>
       <c r="N248">
-        <v>9.2191964749308186E-2</v>
+        <v>9.2419352015981532E-2</v>
       </c>
       <c r="O248" t="s">
         <v>54</v>
@@ -11713,7 +11713,7 @@
         <v>64</v>
       </c>
       <c r="N249">
-        <v>0.11502984163809608</v>
+        <v>0.11435406596281525</v>
       </c>
       <c r="O249" t="s">
         <v>54</v>
@@ -11751,7 +11751,7 @@
         <v>65</v>
       </c>
       <c r="N250">
-        <v>6.9727353824019983E-2</v>
+        <v>6.9489827684403635E-2</v>
       </c>
       <c r="O250" t="s">
         <v>54</v>
@@ -14057,7 +14057,7 @@
         <v>53</v>
       </c>
       <c r="I311">
-        <v>5.6575345499603767E-2</v>
+        <v>5.6814000255900568E-2</v>
       </c>
       <c r="J311" t="s">
         <v>54</v>
@@ -14095,7 +14095,7 @@
         <v>55</v>
       </c>
       <c r="I312">
-        <v>9.9654012159200334E-2</v>
+        <v>9.8828398077766624E-2</v>
       </c>
       <c r="J312" t="s">
         <v>54</v>
@@ -14133,7 +14133,7 @@
         <v>56</v>
       </c>
       <c r="I313">
-        <v>5.1201124223323097E-2</v>
+        <v>5.149279136994294E-2</v>
       </c>
       <c r="J313" t="s">
         <v>54</v>
@@ -14171,7 +14171,7 @@
         <v>57</v>
       </c>
       <c r="I314">
-        <v>6.4781053688715035E-2</v>
+        <v>6.4084880866639729E-2</v>
       </c>
       <c r="J314" t="s">
         <v>54</v>
@@ -14209,7 +14209,7 @@
         <v>58</v>
       </c>
       <c r="I315">
-        <v>9.3468682413901633E-2</v>
+        <v>9.2675940621917405E-2</v>
       </c>
       <c r="J315" t="s">
         <v>54</v>
@@ -14247,7 +14247,7 @@
         <v>59</v>
       </c>
       <c r="I316">
-        <v>5.2381027981142372E-2</v>
+        <v>5.2319239683653783E-2</v>
       </c>
       <c r="J316" t="s">
         <v>54</v>
@@ -14285,7 +14285,7 @@
         <v>60</v>
       </c>
       <c r="I317">
-        <v>9.4436542584151351E-2</v>
+        <v>9.5155186937174951E-2</v>
       </c>
       <c r="J317" t="s">
         <v>54</v>
@@ -14323,7 +14323,7 @@
         <v>61</v>
       </c>
       <c r="I318">
-        <v>0.12288652159386768</v>
+        <v>0.12434882020953973</v>
       </c>
       <c r="J318" t="s">
         <v>54</v>
@@ -14361,7 +14361,7 @@
         <v>62</v>
       </c>
       <c r="I319">
-        <v>6.7858644711248264E-2</v>
+        <v>6.8761551839733037E-2</v>
       </c>
       <c r="J319" t="s">
         <v>54</v>
@@ -14399,7 +14399,7 @@
         <v>63</v>
       </c>
       <c r="I320">
-        <v>9.0775739317214221E-2</v>
+        <v>9.0458748555581017E-2</v>
       </c>
       <c r="J320" t="s">
         <v>54</v>
@@ -14437,7 +14437,7 @@
         <v>64</v>
       </c>
       <c r="I321">
-        <v>0.13424007681549427</v>
+        <v>0.13340686703086105</v>
       </c>
       <c r="J321" t="s">
         <v>54</v>
@@ -14475,7 +14475,7 @@
         <v>65</v>
       </c>
       <c r="I322">
-        <v>7.1741229012140278E-2</v>
+        <v>7.1653574551286889E-2</v>
       </c>
       <c r="J322" t="s">
         <v>54</v>
@@ -14501,7 +14501,7 @@
         <v>53</v>
       </c>
       <c r="D323">
-        <v>6.2365004603211803E-3</v>
+        <v>6.2269964629059569E-3</v>
       </c>
       <c r="E323" t="s">
         <v>54</v>
@@ -14539,7 +14539,7 @@
         <v>55</v>
       </c>
       <c r="D324">
-        <v>0.30998254452307505</v>
+        <v>0.31019165352597583</v>
       </c>
       <c r="E324" t="s">
         <v>54</v>
@@ -14577,7 +14577,7 @@
         <v>56</v>
       </c>
       <c r="D325">
-        <v>1.2164815228971655E-2</v>
+        <v>1.2036241762535644E-2</v>
       </c>
       <c r="E325" t="s">
         <v>54</v>
@@ -14615,7 +14615,7 @@
         <v>57</v>
       </c>
       <c r="D326">
-        <v>3.5214815238628219E-4</v>
+        <v>3.5789303447088749E-4</v>
       </c>
       <c r="E326" t="s">
         <v>54</v>
@@ -14653,7 +14653,7 @@
         <v>58</v>
       </c>
       <c r="D327">
-        <v>0.2318905745278686</v>
+        <v>0.23226550602528137</v>
       </c>
       <c r="E327" t="s">
         <v>54</v>
@@ -14691,7 +14691,7 @@
         <v>59</v>
       </c>
       <c r="D328">
-        <v>2.2539270660570637E-3</v>
+        <v>2.2578734802393015E-3</v>
       </c>
       <c r="E328" t="s">
         <v>54</v>
@@ -14767,7 +14767,7 @@
         <v>61</v>
       </c>
       <c r="D330">
-        <v>0.16335896438294761</v>
+        <v>0.16311221002237686</v>
       </c>
       <c r="E330" t="s">
         <v>54</v>
@@ -14805,7 +14805,7 @@
         <v>62</v>
       </c>
       <c r="D331">
-        <v>6.1961840755985379E-5</v>
+        <v>6.2072713591545647E-5</v>
       </c>
       <c r="E331" t="s">
         <v>54</v>
@@ -14843,7 +14843,7 @@
         <v>63</v>
       </c>
       <c r="D332">
-        <v>5.1594104389922754E-3</v>
+        <v>5.1712255883452195E-3</v>
       </c>
       <c r="E332" t="s">
         <v>54</v>
@@ -14881,7 +14881,7 @@
         <v>64</v>
       </c>
       <c r="D333">
-        <v>0.26412435987568106</v>
+        <v>0.26393910469480864</v>
       </c>
       <c r="E333" t="s">
         <v>54</v>
@@ -14919,7 +14919,7 @@
         <v>65</v>
       </c>
       <c r="D334">
-        <v>4.4147935029442784E-3</v>
+        <v>4.379222689467905E-3</v>
       </c>
       <c r="E334" t="s">
         <v>54</v>
@@ -25013,7 +25013,7 @@
         <v>53</v>
       </c>
       <c r="N599">
-        <v>6.8060022084858493E-2</v>
+        <v>6.8742718398902752E-2</v>
       </c>
       <c r="O599" t="s">
         <v>54</v>
@@ -25051,7 +25051,7 @@
         <v>55</v>
       </c>
       <c r="N600">
-        <v>9.2882116592152647E-2</v>
+        <v>9.3799245664047418E-2</v>
       </c>
       <c r="O600" t="s">
         <v>54</v>
@@ -25089,7 +25089,7 @@
         <v>56</v>
       </c>
       <c r="N601">
-        <v>5.5264698221030126E-2</v>
+        <v>5.647663127112381E-2</v>
       </c>
       <c r="O601" t="s">
         <v>54</v>
@@ -25127,7 +25127,7 @@
         <v>57</v>
       </c>
       <c r="N602">
-        <v>7.6002075341383674E-2</v>
+        <v>7.5642477592911664E-2</v>
       </c>
       <c r="O602" t="s">
         <v>54</v>
@@ -25165,7 +25165,7 @@
         <v>58</v>
       </c>
       <c r="N603">
-        <v>9.1525457044012284E-2</v>
+        <v>9.0969428261153229E-2</v>
       </c>
       <c r="O603" t="s">
         <v>54</v>
@@ -25203,7 +25203,7 @@
         <v>59</v>
       </c>
       <c r="N604">
-        <v>5.6993247250659143E-2</v>
+        <v>5.7184717118323465E-2</v>
       </c>
       <c r="O604" t="s">
         <v>54</v>
@@ -25241,7 +25241,7 @@
         <v>60</v>
       </c>
       <c r="N605">
-        <v>9.6236627406315681E-2</v>
+        <v>9.5235073906446213E-2</v>
       </c>
       <c r="O605" t="s">
         <v>54</v>
@@ -25279,7 +25279,7 @@
         <v>61</v>
       </c>
       <c r="N606">
-        <v>0.11823889604004198</v>
+        <v>0.11632516675947875</v>
       </c>
       <c r="O606" t="s">
         <v>54</v>
@@ -25317,7 +25317,7 @@
         <v>62</v>
       </c>
       <c r="N607">
-        <v>7.1231045202933926E-2</v>
+        <v>7.0745169028451627E-2</v>
       </c>
       <c r="O607" t="s">
         <v>54</v>
@@ -25355,7 +25355,7 @@
         <v>63</v>
       </c>
       <c r="N608">
-        <v>9.0324496324787756E-2</v>
+        <v>9.0644143958785242E-2</v>
       </c>
       <c r="O608" t="s">
         <v>54</v>
@@ -25393,7 +25393,7 @@
         <v>64</v>
       </c>
       <c r="N609">
-        <v>0.11351741797053017</v>
+        <v>0.11414568641537574</v>
       </c>
       <c r="O609" t="s">
         <v>54</v>
@@ -25431,7 +25431,7 @@
         <v>65</v>
       </c>
       <c r="N610">
-        <v>6.9723900521297344E-2</v>
+        <v>7.0089541625000001E-2</v>
       </c>
       <c r="O610" t="s">
         <v>54</v>
@@ -37601,7 +37601,7 @@
         <v>53</v>
       </c>
       <c r="I1067">
-        <v>5.7182885810619422E-2</v>
+        <v>5.6036415593357661E-2</v>
       </c>
       <c r="J1067" t="s">
         <v>54</v>
@@ -37627,7 +37627,7 @@
         <v>55</v>
       </c>
       <c r="I1068">
-        <v>0.10343786175092082</v>
+        <v>0.10298166935120716</v>
       </c>
       <c r="J1068" t="s">
         <v>54</v>
@@ -37653,7 +37653,7 @@
         <v>56</v>
       </c>
       <c r="I1069">
-        <v>5.1780233021949597E-2</v>
+        <v>5.0604989301660526E-2</v>
       </c>
       <c r="J1069" t="s">
         <v>54</v>
@@ -37679,7 +37679,7 @@
         <v>57</v>
       </c>
       <c r="I1070">
-        <v>6.8289082573685031E-2</v>
+        <v>6.7541088648855094E-2</v>
       </c>
       <c r="J1070" t="s">
         <v>54</v>
@@ -37705,7 +37705,7 @@
         <v>58</v>
       </c>
       <c r="I1071">
-        <v>9.6355333073555316E-2</v>
+        <v>9.6398621901010978E-2</v>
       </c>
       <c r="J1071" t="s">
         <v>54</v>
@@ -37731,7 +37731,7 @@
         <v>59</v>
       </c>
       <c r="I1072">
-        <v>5.2557625242657662E-2</v>
+        <v>5.2623261535399764E-2</v>
       </c>
       <c r="J1072" t="s">
         <v>54</v>
@@ -37757,7 +37757,7 @@
         <v>60</v>
       </c>
       <c r="I1073">
-        <v>8.8210191413727768E-2</v>
+        <v>9.0874323271796509E-2</v>
       </c>
       <c r="J1073" t="s">
         <v>54</v>
@@ -37783,7 +37783,7 @@
         <v>61</v>
       </c>
       <c r="I1074">
-        <v>0.1156604636364115</v>
+        <v>0.11687703517770792</v>
       </c>
       <c r="J1074" t="s">
         <v>54</v>
@@ -37809,7 +37809,7 @@
         <v>62</v>
       </c>
       <c r="I1075">
-        <v>6.4527333787363056E-2</v>
+        <v>6.4452427168793805E-2</v>
       </c>
       <c r="J1075" t="s">
         <v>54</v>
@@ -37835,7 +37835,7 @@
         <v>63</v>
       </c>
       <c r="I1076">
-        <v>9.398607521895988E-2</v>
+        <v>9.2445687853348113E-2</v>
       </c>
       <c r="J1076" t="s">
         <v>54</v>
@@ -37861,7 +37861,7 @@
         <v>64</v>
       </c>
       <c r="I1077">
-        <v>0.13490022184628647</v>
+        <v>0.13684718162202592</v>
       </c>
       <c r="J1077" t="s">
         <v>54</v>
@@ -37887,7 +37887,7 @@
         <v>65</v>
       </c>
       <c r="I1078">
-        <v>7.3112692623867007E-2</v>
+        <v>7.2317298574839164E-2</v>
       </c>
       <c r="J1078" t="s">
         <v>54</v>
@@ -37901,7 +37901,7 @@
         <v>53</v>
       </c>
       <c r="D1079">
-        <v>5.7204531478930384E-3</v>
+        <v>6.1695156688371996E-3</v>
       </c>
       <c r="E1079" t="s">
         <v>54</v>
@@ -37927,7 +37927,7 @@
         <v>55</v>
       </c>
       <c r="D1080">
-        <v>0.31883458015108646</v>
+        <v>0.31099680584404682</v>
       </c>
       <c r="E1080" t="s">
         <v>54</v>
@@ -37953,7 +37953,7 @@
         <v>56</v>
       </c>
       <c r="D1081">
-        <v>1.4191602921648273E-2</v>
+        <v>1.3369116577792462E-2</v>
       </c>
       <c r="E1081" t="s">
         <v>54</v>
@@ -37979,7 +37979,7 @@
         <v>57</v>
       </c>
       <c r="D1082">
-        <v>2.2868801901400177E-4</v>
+        <v>2.9031670996052813E-4</v>
       </c>
       <c r="E1082" t="s">
         <v>54</v>
@@ -38005,7 +38005,7 @@
         <v>58</v>
       </c>
       <c r="D1083">
-        <v>0.22737312454370648</v>
+        <v>0.22868429725723294</v>
       </c>
       <c r="E1083" t="s">
         <v>54</v>
@@ -38031,7 +38031,7 @@
         <v>59</v>
       </c>
       <c r="D1084">
-        <v>2.556611684114125E-3</v>
+        <v>2.3025324417374651E-3</v>
       </c>
       <c r="E1084" t="s">
         <v>54</v>
@@ -38083,7 +38083,7 @@
         <v>61</v>
       </c>
       <c r="D1086">
-        <v>0.1534660000476383</v>
+        <v>0.16230612528795976</v>
       </c>
       <c r="E1086" t="s">
         <v>54</v>
@@ -38109,7 +38109,7 @@
         <v>62</v>
       </c>
       <c r="D1087">
-        <v>1.2424454093466815E-4</v>
+        <v>7.6310869983735774E-5</v>
       </c>
       <c r="E1087" t="s">
         <v>54</v>
@@ -38135,7 +38135,7 @@
         <v>63</v>
       </c>
       <c r="D1088">
-        <v>4.6765835434261528E-3</v>
+        <v>4.9796037981650514E-3</v>
       </c>
       <c r="E1088" t="s">
         <v>54</v>
@@ -38161,7 +38161,7 @@
         <v>64</v>
       </c>
       <c r="D1089">
-        <v>0.26779601781357854</v>
+        <v>0.26606635755568669</v>
       </c>
       <c r="E1089" t="s">
         <v>54</v>
@@ -38187,7 +38187,7 @@
         <v>65</v>
       </c>
       <c r="D1090">
-        <v>5.032093586958105E-3</v>
+        <v>4.7590179885950963E-3</v>
       </c>
       <c r="E1090" t="s">
         <v>54</v>
@@ -40395,7 +40395,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC8AE6EA-4E53-4A7C-85A6-B565D211B7C4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{567156C8-E632-4588-B55F-0C8AEAF63B4E}">
   <dimension ref="B9:CI256"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41363,40 +41363,40 @@
         <v>31</v>
       </c>
       <c r="D14">
-        <v>0.80784047780567536</v>
+        <v>0.80782734756958385</v>
       </c>
       <c r="E14">
-        <v>0.16530035278488545</v>
+        <v>0.16531047268121599</v>
       </c>
       <c r="F14">
-        <v>0.67876386937128275</v>
+        <v>0.67871527175788948</v>
       </c>
       <c r="G14">
-        <v>0.9698091497930883</v>
+        <v>0.96981922900865924</v>
       </c>
       <c r="H14">
-        <v>0.24418340601494462</v>
+        <v>0.24421652381748282</v>
       </c>
       <c r="I14">
-        <v>0.88972129387215482</v>
+        <v>0.88969898428864436</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0.30487421442522772</v>
+        <v>0.30490143044404594</v>
       </c>
       <c r="L14">
-        <v>0.96739130434782594</v>
+        <v>0.96739130434782605</v>
       </c>
       <c r="M14">
-        <v>0.85257520869536196</v>
+        <v>0.85254187577587393</v>
       </c>
       <c r="N14">
-        <v>0.21060685456190525</v>
+        <v>0.21053894754540778</v>
       </c>
       <c r="O14">
-        <v>0.78556490244133192</v>
+        <v>0.78547942639345458</v>
       </c>
       <c r="Q14" t="s">
         <v>314</v>
@@ -41405,40 +41405,40 @@
         <v>557</v>
       </c>
       <c r="S14">
-        <v>0.67981257633566561</v>
+        <v>0.67976477667620161</v>
       </c>
       <c r="T14">
-        <v>8.3939756257385076E-2</v>
+        <v>8.3956266581999672E-2</v>
       </c>
       <c r="U14">
-        <v>0.53806297189622398</v>
+        <v>0.53797616943830628</v>
       </c>
       <c r="V14">
-        <v>0.94213796481257928</v>
+        <v>0.94214775644183579</v>
       </c>
       <c r="W14">
-        <v>0.12223096021399302</v>
+        <v>0.12226040330681312</v>
       </c>
       <c r="X14">
-        <v>0.47541144507216521</v>
+        <v>0.4751215751220037</v>
       </c>
       <c r="Y14">
         <v>0</v>
       </c>
       <c r="Z14">
-        <v>0.16725168004285787</v>
+        <v>0.16724626486185595</v>
       </c>
       <c r="AA14">
-        <v>0.93739218606937735</v>
+        <v>0.93736944589472848</v>
       </c>
       <c r="AB14">
-        <v>0.75337435543872822</v>
+        <v>0.75329576045493629</v>
       </c>
       <c r="AC14">
-        <v>0.10415318940148655</v>
+        <v>0.10409259441546932</v>
       </c>
       <c r="AD14">
-        <v>0.65592707464233335</v>
+        <v>0.65579860705908566</v>
       </c>
       <c r="AF14" t="s">
         <v>314</v>
@@ -41450,7 +41450,7 @@
         <v>0</v>
       </c>
       <c r="AI14">
-        <v>8.4903297276582596E-3</v>
+        <v>8.4948813083785615E-3</v>
       </c>
       <c r="AJ14">
         <v>0</v>
@@ -41459,16 +41459,16 @@
         <v>0</v>
       </c>
       <c r="AL14">
-        <v>1.7201325208341167E-2</v>
+        <v>1.722302682916288E-2</v>
       </c>
       <c r="AM14">
-        <v>0.33162401734440061</v>
+        <v>0.33188785471221943</v>
       </c>
       <c r="AN14">
         <v>0</v>
       </c>
       <c r="AO14">
-        <v>1.2575156358342514E-2</v>
+        <v>1.2621681249327634E-2</v>
       </c>
       <c r="AP14">
         <v>0</v>
@@ -41477,7 +41477,7 @@
         <v>0</v>
       </c>
       <c r="AR14">
-        <v>1.6007645115395035E-2</v>
+        <v>1.6031429252345911E-2</v>
       </c>
       <c r="AS14">
         <v>0</v>
@@ -41528,40 +41528,40 @@
         <v>314</v>
       </c>
       <c r="BS14">
-        <v>9.3903656030910436E-3</v>
+        <v>9.3816551008878875E-3</v>
       </c>
       <c r="BT14">
-        <v>0.48135783736553711</v>
+        <v>0.48105959635944018</v>
       </c>
       <c r="BU14">
-        <v>3.6840799247507737E-2</v>
+        <v>3.6826024375317068E-2</v>
       </c>
       <c r="BV14">
-        <v>2.8796496033422017E-4</v>
+        <v>2.8755268109367511E-4</v>
       </c>
       <c r="BW14">
-        <v>0.33409136871016931</v>
+        <v>0.33383169895708148</v>
       </c>
       <c r="BX14">
-        <v>7.2416801532378169E-3</v>
+        <v>7.2373796860401339E-3</v>
       </c>
       <c r="BY14">
         <v>0</v>
       </c>
       <c r="BZ14">
-        <v>0.22727289401653736</v>
+        <v>0.22699341503977166</v>
       </c>
       <c r="CA14">
-        <v>5.8212142024592476E-4</v>
+        <v>5.8093668919658933E-4</v>
       </c>
       <c r="CB14">
-        <v>7.8811105563806466E-3</v>
+        <v>7.8735729610752772E-3</v>
       </c>
       <c r="CC14">
-        <v>0.40164300410702297</v>
+        <v>0.40132585954008559</v>
       </c>
       <c r="CD14">
-        <v>1.390494245326953E-2</v>
+        <v>1.3894024674995314E-2</v>
       </c>
       <c r="CF14" t="s">
         <v>314</v>
@@ -41573,7 +41573,7 @@
         <v>572</v>
       </c>
       <c r="CI14">
-        <v>0.45503008987076232</v>
+        <v>0.45421945168319344</v>
       </c>
     </row>
     <row r="15" spans="2:87" x14ac:dyDescent="0.45">
@@ -46446,40 +46446,40 @@
         <v>31</v>
       </c>
       <c r="D37">
-        <v>0.80138118898076605</v>
+        <v>0.80148197715800296</v>
       </c>
       <c r="E37">
-        <v>0.16009690318799891</v>
+        <v>0.16001962401162614</v>
       </c>
       <c r="F37">
-        <v>0.69189879380694119</v>
+        <v>0.69322368663665657</v>
       </c>
       <c r="G37">
-        <v>0.95914325306427606</v>
+        <v>0.95913740309765005</v>
       </c>
       <c r="H37">
-        <v>0.22346724432749415</v>
+        <v>0.22419528203024849</v>
       </c>
       <c r="I37">
-        <v>0.90820884050319717</v>
+        <v>0.90842323931314395</v>
       </c>
       <c r="J37">
         <v>0</v>
       </c>
       <c r="K37">
-        <v>0.29520988533663112</v>
+        <v>0.29579851492741471</v>
       </c>
       <c r="L37">
-        <v>0.98620534078504685</v>
+        <v>0.98605645749949733</v>
       </c>
       <c r="M37">
-        <v>0.84171325500059391</v>
+        <v>0.84211288144972885</v>
       </c>
       <c r="N37">
-        <v>0.20550489689196319</v>
+        <v>0.20600797497738563</v>
       </c>
       <c r="O37">
-        <v>0.79204915779888707</v>
+        <v>0.79234780553262441</v>
       </c>
       <c r="Q37" t="s">
         <v>337</v>
@@ -46488,40 +46488,40 @@
         <v>557</v>
       </c>
       <c r="S37">
-        <v>0.66463148405887651</v>
+        <v>0.66611775944488072</v>
       </c>
       <c r="T37">
-        <v>8.217465375641253E-2</v>
+        <v>8.2122836575313385E-2</v>
       </c>
       <c r="U37">
-        <v>0.56749142061051427</v>
+        <v>0.56952921909009657</v>
       </c>
       <c r="V37">
-        <v>0.92018794172423668</v>
+        <v>0.92004212851486578</v>
       </c>
       <c r="W37">
-        <v>0.1141416329956058</v>
+        <v>0.11513734780310124</v>
       </c>
       <c r="X37">
-        <v>0.59623623767229872</v>
+        <v>0.59993298348591451</v>
       </c>
       <c r="Y37">
         <v>0</v>
       </c>
       <c r="Z37">
-        <v>0.16328587965502628</v>
+        <v>0.1642313099785212</v>
       </c>
       <c r="AA37">
-        <v>0.97369911363741046</v>
+        <v>0.97355211836454025</v>
       </c>
       <c r="AB37">
-        <v>0.73502587918861928</v>
+        <v>0.7353231934633967</v>
       </c>
       <c r="AC37">
-        <v>0.10313565158651135</v>
+        <v>0.10311421420837714</v>
       </c>
       <c r="AD37">
-        <v>0.66137551298855635</v>
+        <v>0.6619462672334927</v>
       </c>
       <c r="AF37" t="s">
         <v>337</v>
@@ -46533,7 +46533,7 @@
         <v>0</v>
       </c>
       <c r="AI37">
-        <v>6.5240785661260358E-3</v>
+        <v>6.3590862275437138E-3</v>
       </c>
       <c r="AJ37">
         <v>0</v>
@@ -46542,16 +46542,16 @@
         <v>0</v>
       </c>
       <c r="AL37">
-        <v>1.2248586807940895E-2</v>
+        <v>1.1994227121638513E-2</v>
       </c>
       <c r="AM37">
-        <v>0.24098530026167347</v>
+        <v>0.23791632013768813</v>
       </c>
       <c r="AN37">
         <v>0</v>
       </c>
       <c r="AO37">
-        <v>1.0775110666458096E-2</v>
+        <v>1.0880986102289691E-2</v>
       </c>
       <c r="AP37">
         <v>0</v>
@@ -46560,7 +46560,7 @@
         <v>0</v>
       </c>
       <c r="AR37">
-        <v>1.1273381125909832E-2</v>
+        <v>1.1387939080892693E-2</v>
       </c>
       <c r="AS37">
         <v>0</v>
@@ -46611,40 +46611,40 @@
         <v>337</v>
       </c>
       <c r="BS37">
-        <v>1.2307253982315476E-2</v>
+        <v>1.2387849678703747E-2</v>
       </c>
       <c r="BT37">
-        <v>0.48938136761826528</v>
+        <v>0.49367075743288424</v>
       </c>
       <c r="BU37">
-        <v>3.2008436274678101E-2</v>
+        <v>3.19261791863929E-2</v>
       </c>
       <c r="BV37">
-        <v>6.798299610348053E-4</v>
+        <v>6.9650659948489386E-4</v>
       </c>
       <c r="BW37">
-        <v>0.35813599288220616</v>
+        <v>0.36161521392776086</v>
       </c>
       <c r="BX37">
-        <v>5.8016761377639465E-3</v>
+        <v>5.8588223419457569E-3</v>
       </c>
       <c r="BY37">
         <v>0</v>
       </c>
       <c r="BZ37">
-        <v>0.25229453600954704</v>
+        <v>0.25395013547578377</v>
       </c>
       <c r="CA37">
-        <v>1.5949164388659448E-4</v>
+        <v>1.6106881293313373E-4</v>
       </c>
       <c r="CB37">
-        <v>1.0069812859310552E-2</v>
+        <v>1.0174472647107302E-2</v>
       </c>
       <c r="CC37">
-        <v>0.41240105348979128</v>
+        <v>0.41544367467111887</v>
       </c>
       <c r="CD37">
-        <v>1.148868846232802E-2</v>
+        <v>1.1488258301217859E-2</v>
       </c>
       <c r="CF37" t="s">
         <v>337</v>
@@ -46656,7 +46656,7 @@
         <v>572</v>
       </c>
       <c r="CI37">
-        <v>0.43904961189233921</v>
+        <v>0.44524746815500882</v>
       </c>
     </row>
     <row r="38" spans="2:87" x14ac:dyDescent="0.45">
@@ -60369,40 +60369,40 @@
         <v>31</v>
       </c>
       <c r="D100">
-        <v>0.80322187577286719</v>
+        <v>0.80180358833509657</v>
       </c>
       <c r="E100">
-        <v>0.1811409724459476</v>
+        <v>0.17758922203852481</v>
       </c>
       <c r="F100">
-        <v>0.68318506092200948</v>
+        <v>0.68692495261916786</v>
       </c>
       <c r="G100">
-        <v>0.96467391304347816</v>
+        <v>0.96146389445907787</v>
       </c>
       <c r="H100">
-        <v>0.2485737852825198</v>
+        <v>0.23937664718992027</v>
       </c>
       <c r="I100">
-        <v>0.90232848553943701</v>
+        <v>0.90582058048315339</v>
       </c>
       <c r="J100">
         <v>0</v>
       </c>
       <c r="K100">
-        <v>0.32155582498860452</v>
+        <v>0.31267449390888896</v>
       </c>
       <c r="L100">
-        <v>0.97996180836396096</v>
+        <v>0.98456262624931612</v>
       </c>
       <c r="M100">
-        <v>0.84638777437543455</v>
+        <v>0.84428201223591293</v>
       </c>
       <c r="N100">
-        <v>0.21857720505490111</v>
+        <v>0.2151603959024446</v>
       </c>
       <c r="O100">
-        <v>0.78807047342106085</v>
+        <v>0.79194262978710828</v>
       </c>
       <c r="Q100" t="s">
         <v>400</v>
@@ -60411,40 +60411,40 @@
         <v>557</v>
       </c>
       <c r="S100">
-        <v>0.66828879250166651</v>
+        <v>0.66329074221523887</v>
       </c>
       <c r="T100">
-        <v>9.4782448854091844E-2</v>
+        <v>9.2704501542109422E-2</v>
       </c>
       <c r="U100">
-        <v>0.54745499904299477</v>
+        <v>0.55501771000840305</v>
       </c>
       <c r="V100">
-        <v>0.93059575850661669</v>
+        <v>0.92724888806073857</v>
       </c>
       <c r="W100">
-        <v>0.12634024393207891</v>
+        <v>0.12351619295670867</v>
       </c>
       <c r="X100">
-        <v>0.49404632468008192</v>
+        <v>0.57142609872714156</v>
       </c>
       <c r="Y100">
         <v>0</v>
       </c>
       <c r="Z100">
-        <v>0.17830813056108552</v>
+        <v>0.1750918821772933</v>
       </c>
       <c r="AA100">
-        <v>0.96220887705301961</v>
+        <v>0.97029360268048559</v>
       </c>
       <c r="AB100">
-        <v>0.7411000260892795</v>
+        <v>0.73747768914449507</v>
       </c>
       <c r="AC100">
-        <v>0.10812953173291098</v>
+        <v>0.11098157010687887</v>
       </c>
       <c r="AD100">
-        <v>0.65440321282744573</v>
+        <v>0.65960387437423007</v>
       </c>
       <c r="AF100" t="s">
         <v>400</v>
@@ -60456,7 +60456,7 @@
         <v>0</v>
       </c>
       <c r="AI100">
-        <v>9.5353278814970747E-3</v>
+        <v>9.8724712369556017E-3</v>
       </c>
       <c r="AJ100">
         <v>0</v>
@@ -60465,16 +60465,16 @@
         <v>0</v>
       </c>
       <c r="AL100">
-        <v>1.9920040920160219E-2</v>
+        <v>1.7245374291577562E-2</v>
       </c>
       <c r="AM100">
-        <v>0.33309678822505773</v>
+        <v>0.2616288931887541</v>
       </c>
       <c r="AN100">
         <v>0</v>
       </c>
       <c r="AO100">
-        <v>1.3673751151728482E-2</v>
+        <v>1.2196802811207578E-2</v>
       </c>
       <c r="AP100">
         <v>0</v>
@@ -60483,7 +60483,7 @@
         <v>0</v>
       </c>
       <c r="AR100">
-        <v>1.6094780582165371E-2</v>
+        <v>1.2989935186781E-2</v>
       </c>
       <c r="AS100">
         <v>0</v>
@@ -60534,40 +60534,40 @@
         <v>400</v>
       </c>
       <c r="BS100">
-        <v>1.0147442530351698E-2</v>
+        <v>1.1357921541486923E-2</v>
       </c>
       <c r="BT100">
-        <v>0.45246143899821795</v>
+        <v>0.45802977219383212</v>
       </c>
       <c r="BU100">
-        <v>3.3565749970708388E-2</v>
+        <v>3.2816271772416784E-2</v>
       </c>
       <c r="BV100">
-        <v>3.9684806037144313E-4</v>
+        <v>5.2284686510298696E-4</v>
       </c>
       <c r="BW100">
-        <v>0.31565303279045809</v>
+        <v>0.32947980964782991</v>
       </c>
       <c r="BX100">
-        <v>5.9154032487175739E-3</v>
+        <v>5.5290048311906889E-3</v>
       </c>
       <c r="BY100">
         <v>0</v>
       </c>
       <c r="BZ100">
-        <v>0.21305072199043434</v>
+        <v>0.23384461419491903</v>
       </c>
       <c r="CA100">
-        <v>2.8747289455302041E-4</v>
+        <v>1.8324309406648841E-4</v>
       </c>
       <c r="CB100">
-        <v>8.2045729646254423E-3</v>
+        <v>9.0665842059523653E-3</v>
       </c>
       <c r="CC100">
-        <v>0.37585591231464921</v>
+        <v>0.38755099930457659</v>
       </c>
       <c r="CD100">
-        <v>1.1771037158684577E-2</v>
+        <v>1.1553271861277862E-2</v>
       </c>
       <c r="CF100" t="s">
         <v>400</v>
@@ -60579,7 +60579,7 @@
         <v>572</v>
       </c>
       <c r="CI100">
-        <v>0.41834200049529696</v>
+        <v>0.42454320653884547</v>
       </c>
     </row>
     <row r="101" spans="2:87" x14ac:dyDescent="0.45">
@@ -62579,40 +62579,40 @@
         <v>31</v>
       </c>
       <c r="D110">
-        <v>0.25545258410124155</v>
+        <v>0.28156776667674605</v>
       </c>
       <c r="E110">
-        <v>0.26890595704582881</v>
+        <v>0.270133613435878</v>
       </c>
       <c r="F110">
-        <v>0.24220696079883339</v>
+        <v>0.26627396018090177</v>
       </c>
       <c r="G110">
-        <v>0.29668601089242791</v>
+        <v>0.27941563044143725</v>
       </c>
       <c r="H110">
-        <v>0.34917443238149132</v>
+        <v>0.30169838483982636</v>
       </c>
       <c r="I110">
-        <v>0.32500493039964534</v>
+        <v>0.299464740322815</v>
       </c>
       <c r="J110">
-        <v>0.24273328467895036</v>
+        <v>0.21279702409028417</v>
       </c>
       <c r="K110">
-        <v>0.24920955342552367</v>
+        <v>0.21001143384826426</v>
       </c>
       <c r="L110">
-        <v>0.23661501714508476</v>
+        <v>0.21060410464706844</v>
       </c>
       <c r="M110">
-        <v>0.22394781739777966</v>
+        <v>0.22831659190848427</v>
       </c>
       <c r="N110">
-        <v>0.23857223447477086</v>
+        <v>0.23794535251877783</v>
       </c>
       <c r="O110">
-        <v>0.21202861210868384</v>
+        <v>0.22464127538476164</v>
       </c>
       <c r="Q110" t="s">
         <v>410</v>
@@ -62621,40 +62621,40 @@
         <v>557</v>
       </c>
       <c r="S110">
-        <v>1.0423256550638835E-2</v>
+        <v>3.1779570200261703E-2</v>
       </c>
       <c r="T110">
-        <v>2.1860274746599923E-2</v>
+        <v>2.171320494168234E-2</v>
       </c>
       <c r="U110">
-        <v>1.3198588126147135E-2</v>
+        <v>1.4769572734059455E-2</v>
       </c>
       <c r="V110">
-        <v>1.5761891332468653E-2</v>
+        <v>1.5424967572190583E-2</v>
       </c>
       <c r="W110">
-        <v>9.6124797687629181E-3</v>
+        <v>8.6710497150679321E-3</v>
       </c>
       <c r="X110">
-        <v>1.6860477965807405E-2</v>
+        <v>1.5327406070437744E-2</v>
       </c>
       <c r="Y110">
-        <v>8.1207394335617213E-3</v>
+        <v>7.7491888411498943E-3</v>
       </c>
       <c r="Z110">
-        <v>6.4166962742277442E-3</v>
+        <v>9.1834910196380553E-3</v>
       </c>
       <c r="AA110">
-        <v>8.5239593730156559E-3</v>
+        <v>1.3520009048754361E-2</v>
       </c>
       <c r="AB110">
-        <v>1.0668540230402051E-2</v>
+        <v>1.064171967796626E-2</v>
       </c>
       <c r="AC110">
-        <v>1.3479646739894406E-2</v>
+        <v>1.4458750099124262E-2</v>
       </c>
       <c r="AD110">
-        <v>1.5599209883798499E-2</v>
+        <v>7.3743586976187086E-3</v>
       </c>
       <c r="AF110" t="s">
         <v>410</v>
@@ -62663,40 +62663,40 @@
         <v>558</v>
       </c>
       <c r="AH110">
-        <v>1.6608798966025805E-2</v>
+        <v>2.8056896536870587E-2</v>
       </c>
       <c r="AI110">
-        <v>1.6551697696726871E-2</v>
+        <v>3.4781336018763043E-2</v>
       </c>
       <c r="AJ110">
-        <v>1.8492645441087335E-2</v>
+        <v>2.1632940163948507E-2</v>
       </c>
       <c r="AK110">
-        <v>2.0388159444574758E-2</v>
+        <v>2.7848348856311801E-2</v>
       </c>
       <c r="AL110">
-        <v>2.4786768593571061E-2</v>
+        <v>1.8219762368656425E-2</v>
       </c>
       <c r="AM110">
-        <v>1.966594861747608E-2</v>
+        <v>1.1430946297694797E-2</v>
       </c>
       <c r="AN110">
-        <v>1.0772866000068196E-2</v>
+        <v>1.9470920316315893E-2</v>
       </c>
       <c r="AO110">
-        <v>1.0019354879968698E-2</v>
+        <v>1.1657568249847585E-2</v>
       </c>
       <c r="AP110">
-        <v>9.6047595513057658E-3</v>
+        <v>1.2571785541750147E-2</v>
       </c>
       <c r="AQ110">
-        <v>1.5540955820309753E-2</v>
+        <v>1.3972629067302345E-2</v>
       </c>
       <c r="AR110">
-        <v>1.4482001437432467E-2</v>
+        <v>1.7715876013875212E-2</v>
       </c>
       <c r="AS110">
-        <v>1.6099263635047146E-2</v>
+        <v>1.4295144431556753E-2</v>
       </c>
       <c r="AU110" t="s">
         <v>410</v>
@@ -62705,79 +62705,79 @@
         <v>559</v>
       </c>
       <c r="AW110">
-        <v>0.10669206672075701</v>
+        <v>0.10647916363712889</v>
       </c>
       <c r="AX110">
-        <v>0.11273592462692363</v>
+        <v>9.9773369156785724E-2</v>
       </c>
       <c r="AY110">
-        <v>9.5319958047612868E-2</v>
+        <v>0.12154336782203902</v>
       </c>
       <c r="AZ110">
-        <v>0.13135459145547446</v>
+        <v>0.11521317911660338</v>
       </c>
       <c r="BA110">
-        <v>0.1778973159704364</v>
+        <v>0.14447923830803311</v>
       </c>
       <c r="BB110">
-        <v>0.14512707650369266</v>
+        <v>0.14321150416089248</v>
       </c>
       <c r="BC110">
-        <v>0.10007181074165984</v>
+        <v>8.172982140126403E-2</v>
       </c>
       <c r="BD110">
-        <v>0.11106254321883927</v>
+        <v>8.1381043964026262E-2</v>
       </c>
       <c r="BE110">
-        <v>9.3491532222720011E-2</v>
+        <v>8.1166884585464741E-2</v>
       </c>
       <c r="BF110">
-        <v>8.0413817706114499E-2</v>
+        <v>9.8961099471135405E-2</v>
       </c>
       <c r="BG110">
-        <v>8.8974309722358119E-2</v>
+        <v>8.4366305727994306E-2</v>
       </c>
       <c r="BH110">
-        <v>6.8399269042979396E-2</v>
+        <v>9.5693881380100029E-2</v>
       </c>
       <c r="BR110" t="s">
         <v>410</v>
       </c>
       <c r="BS110">
-        <v>0.50948780778841574</v>
+        <v>0.46350163873527572</v>
       </c>
       <c r="BT110">
-        <v>0.51831009940411543</v>
+        <v>0.49647145083668748</v>
       </c>
       <c r="BU110">
-        <v>0.56718043959808329</v>
+        <v>0.46262913472616846</v>
       </c>
       <c r="BV110">
-        <v>0.47517133032797804</v>
+        <v>0.51380120873195312</v>
       </c>
       <c r="BW110">
-        <v>0.45200271388487767</v>
+        <v>0.49559121141603474</v>
       </c>
       <c r="BX110">
-        <v>0.4846175773478098</v>
+        <v>0.49630012522885264</v>
       </c>
       <c r="BY110">
-        <v>0.6082295802238995</v>
+        <v>0.618853946142217</v>
       </c>
       <c r="BZ110">
-        <v>0.60666867090953114</v>
+        <v>0.6340426590432906</v>
       </c>
       <c r="CA110">
-        <v>0.62067596487402854</v>
+        <v>0.6104434209059042</v>
       </c>
       <c r="CB110">
-        <v>0.62439753964604994</v>
+        <v>0.60806477565000494</v>
       </c>
       <c r="CC110">
-        <v>0.61775780269220348</v>
+        <v>0.61688845851656826</v>
       </c>
       <c r="CD110">
-        <v>0.64811859181258935</v>
+        <v>0.61190196238219596</v>
       </c>
       <c r="CF110" t="s">
         <v>462</v>
@@ -62800,40 +62800,40 @@
         <v>31</v>
       </c>
       <c r="D111">
-        <v>0.25230361316591315</v>
+        <v>0.24087323171587061</v>
       </c>
       <c r="E111">
-        <v>0.23870093901768191</v>
+        <v>0.24304611375576068</v>
       </c>
       <c r="F111">
-        <v>0.22624873206328922</v>
+        <v>0.22154178077850667</v>
       </c>
       <c r="G111">
-        <v>0.25553297454734414</v>
+        <v>0.27592507554303131</v>
       </c>
       <c r="H111">
-        <v>0.29004652920486523</v>
+        <v>0.31595426392415571</v>
       </c>
       <c r="I111">
-        <v>0.27701793360267124</v>
+        <v>0.29113800086090069</v>
       </c>
       <c r="J111">
-        <v>0.23829326279171462</v>
+        <v>0.24012321755182858</v>
       </c>
       <c r="K111">
-        <v>0.21956381180858628</v>
+        <v>0.23396588330050716</v>
       </c>
       <c r="L111">
-        <v>0.21939173196788239</v>
+        <v>0.22370940023923494</v>
       </c>
       <c r="M111">
-        <v>0.19267317730454844</v>
+        <v>0.20151648124753391</v>
       </c>
       <c r="N111">
-        <v>0.205122760326297</v>
+        <v>0.21458768017615651</v>
       </c>
       <c r="O111">
-        <v>0.19717126614574346</v>
+        <v>0.19450950237641507</v>
       </c>
       <c r="Q111" t="s">
         <v>411</v>
@@ -62842,40 +62842,40 @@
         <v>557</v>
       </c>
       <c r="S111">
-        <v>1.9659061516663863E-2</v>
+        <v>1.1757537560026879E-2</v>
       </c>
       <c r="T111">
-        <v>1.580247491891441E-2</v>
+        <v>1.9598846948821674E-2</v>
       </c>
       <c r="U111">
-        <v>1.2461334041358813E-2</v>
+        <v>1.3208081205324969E-2</v>
       </c>
       <c r="V111">
-        <v>1.8759215875036959E-2</v>
+        <v>1.5585583414856949E-2</v>
       </c>
       <c r="W111">
-        <v>5.9218590422952626E-3</v>
+        <v>6.1028329607277837E-3</v>
       </c>
       <c r="X111">
-        <v>1.4680884320448104E-2</v>
+        <v>1.5827533854798636E-2</v>
       </c>
       <c r="Y111">
-        <v>9.6262060010327E-3</v>
+        <v>8.1073704259225776E-3</v>
       </c>
       <c r="Z111">
-        <v>8.3899973945742549E-3</v>
+        <v>5.5391593904816436E-3</v>
       </c>
       <c r="AA111">
-        <v>9.1399978474006344E-3</v>
+        <v>9.5126296369655236E-3</v>
       </c>
       <c r="AB111">
-        <v>1.2923535816086388E-2</v>
+        <v>1.0815191136341494E-2</v>
       </c>
       <c r="AC111">
-        <v>9.3549391419838392E-3</v>
+        <v>1.0401983069401018E-2</v>
       </c>
       <c r="AD111">
-        <v>8.5334188330184503E-3</v>
+        <v>9.8532435524972695E-3</v>
       </c>
       <c r="AF111" t="s">
         <v>411</v>
@@ -62884,40 +62884,40 @@
         <v>558</v>
       </c>
       <c r="AH111">
-        <v>2.131441495299544E-2</v>
+        <v>1.6274623999171223E-2</v>
       </c>
       <c r="AI111">
-        <v>2.8038017003777269E-2</v>
+        <v>2.0320248981147714E-2</v>
       </c>
       <c r="AJ111">
-        <v>1.3639928529861437E-2</v>
+        <v>1.7325618253347854E-2</v>
       </c>
       <c r="AK111">
-        <v>1.9417657354736165E-2</v>
+        <v>2.1160999573520883E-2</v>
       </c>
       <c r="AL111">
-        <v>2.1738520739859615E-2</v>
+        <v>1.8296279197377991E-2</v>
       </c>
       <c r="AM111">
-        <v>1.4232281344983097E-2</v>
+        <v>1.268187557416469E-2</v>
       </c>
       <c r="AN111">
-        <v>1.4184430392927803E-2</v>
+        <v>1.137379150493641E-2</v>
       </c>
       <c r="AO111">
-        <v>1.012982458562886E-2</v>
+        <v>7.0796597354371767E-3</v>
       </c>
       <c r="AP111">
-        <v>1.9255018061100821E-2</v>
+        <v>1.4348104503470899E-2</v>
       </c>
       <c r="AQ111">
-        <v>1.2780074540450437E-2</v>
+        <v>1.5107241775457863E-2</v>
       </c>
       <c r="AR111">
-        <v>1.2135677919499514E-2</v>
+        <v>1.4376459091294223E-2</v>
       </c>
       <c r="AS111">
-        <v>1.1698341939131983E-2</v>
+        <v>1.1632863161726714E-2</v>
       </c>
       <c r="AU111" t="s">
         <v>411</v>
@@ -62926,79 +62926,79 @@
         <v>559</v>
       </c>
       <c r="AW111">
-        <v>0.10206749876896355</v>
+        <v>0.10203872206647406</v>
       </c>
       <c r="AX111">
-        <v>9.1500650340258158E-2</v>
+        <v>9.6387162060754733E-2</v>
       </c>
       <c r="AY111">
-        <v>0.1043575307738238</v>
+        <v>8.7424063488963644E-2</v>
       </c>
       <c r="AZ111">
-        <v>0.10548535134090987</v>
+        <v>0.11445489117885022</v>
       </c>
       <c r="BA111">
-        <v>0.13738668339047738</v>
+        <v>0.16329462947591769</v>
       </c>
       <c r="BB111">
-        <v>0.12567771914957918</v>
+        <v>0.13312133483161737</v>
       </c>
       <c r="BC111">
-        <v>9.4400664438360454E-2</v>
+        <v>9.844420687579665E-2</v>
       </c>
       <c r="BD111">
-        <v>9.2722390564498158E-2</v>
+        <v>0.10783600367348545</v>
       </c>
       <c r="BE111">
-        <v>8.5358176179365655E-2</v>
+        <v>8.7232271558913124E-2</v>
       </c>
       <c r="BF111">
-        <v>7.2071281297157286E-2</v>
+        <v>7.1321250958809104E-2</v>
       </c>
       <c r="BG111">
-        <v>7.611262868645019E-2</v>
+        <v>8.227943146310078E-2</v>
       </c>
       <c r="BH111">
-        <v>7.8173747797251947E-2</v>
+        <v>7.3287215874702494E-2</v>
       </c>
       <c r="BR111" t="s">
         <v>411</v>
       </c>
       <c r="BS111">
-        <v>0.50396836408501644</v>
+        <v>0.51231350489133543</v>
       </c>
       <c r="BT111">
-        <v>0.53121235105521936</v>
+        <v>0.52859361846278341</v>
       </c>
       <c r="BU111">
-        <v>0.52412862735951959</v>
+        <v>0.56075038594614168</v>
       </c>
       <c r="BV111">
-        <v>0.5211973476102465</v>
+        <v>0.49424943376649549</v>
       </c>
       <c r="BW111">
-        <v>0.49862795052486591</v>
+        <v>0.47081163620467581</v>
       </c>
       <c r="BX111">
-        <v>0.511947475501911</v>
+        <v>0.49881361371693961</v>
       </c>
       <c r="BY111">
-        <v>0.60950864721571829</v>
+        <v>0.608255484422351</v>
       </c>
       <c r="BZ111">
-        <v>0.62542127725565289</v>
+        <v>0.61333585034573135</v>
       </c>
       <c r="CA111">
-        <v>0.61344855263609588</v>
+        <v>0.61938737963400503</v>
       </c>
       <c r="CB111">
-        <v>0.64890780677462945</v>
+        <v>0.64057706540248205</v>
       </c>
       <c r="CC111">
-        <v>0.64655414448764859</v>
+        <v>0.63321845610686756</v>
       </c>
       <c r="CD111">
-        <v>0.64291171489667021</v>
+        <v>0.65125168431742753</v>
       </c>
       <c r="CF111" t="s">
         <v>463</v>
@@ -63010,7 +63010,7 @@
         <v>572</v>
       </c>
       <c r="CI111">
-        <v>0.46788873785474094</v>
+        <v>0.46687687903350239</v>
       </c>
     </row>
     <row r="112" spans="2:87" x14ac:dyDescent="0.45">
@@ -66336,40 +66336,40 @@
         <v>31</v>
       </c>
       <c r="D127">
-        <v>0.2621866368764435</v>
+        <v>0.26096232914081047</v>
       </c>
       <c r="E127">
-        <v>0.2239958496979122</v>
+        <v>0.22591726695844683</v>
       </c>
       <c r="F127">
-        <v>0.22215986941211779</v>
+        <v>0.22081622135063006</v>
       </c>
       <c r="G127">
-        <v>0.27600023067890672</v>
+        <v>0.27615951122091276</v>
       </c>
       <c r="H127">
-        <v>0.29149796969692837</v>
+        <v>0.29301322290715165</v>
       </c>
       <c r="I127">
-        <v>0.26859013168749241</v>
+        <v>0.27134490621377405</v>
       </c>
       <c r="J127">
-        <v>0.22206039876757006</v>
+        <v>0.22534586735683718</v>
       </c>
       <c r="K127">
-        <v>0.23078399176885581</v>
+        <v>0.22914699624095017</v>
       </c>
       <c r="L127">
-        <v>0.22731600294846119</v>
+        <v>0.23194640973930197</v>
       </c>
       <c r="M127">
-        <v>0.21363377730212621</v>
+        <v>0.2126796135599186</v>
       </c>
       <c r="N127">
-        <v>0.21537891339719709</v>
+        <v>0.21698826007624089</v>
       </c>
       <c r="O127">
-        <v>0.21038340361621327</v>
+        <v>0.21359964053097769</v>
       </c>
       <c r="Q127" t="s">
         <v>427</v>
@@ -66378,40 +66378,40 @@
         <v>557</v>
       </c>
       <c r="S127">
-        <v>1.5848958478237342E-2</v>
+        <v>1.920073026379323E-2</v>
       </c>
       <c r="T127">
-        <v>1.4478219010311032E-2</v>
+        <v>1.4857131352692381E-2</v>
       </c>
       <c r="U127">
-        <v>1.6899773873078994E-2</v>
+        <v>1.738373895377426E-2</v>
       </c>
       <c r="V127">
-        <v>1.2458007007533252E-2</v>
+        <v>1.306044378564253E-2</v>
       </c>
       <c r="W127">
-        <v>1.6579565470770379E-2</v>
+        <v>1.6671027835538317E-2</v>
       </c>
       <c r="X127">
-        <v>1.7038622925299129E-2</v>
+        <v>1.5686083776498258E-2</v>
       </c>
       <c r="Y127">
-        <v>8.8484307955620581E-3</v>
+        <v>6.0029591157234E-3</v>
       </c>
       <c r="Z127">
-        <v>9.1957160633112222E-3</v>
+        <v>8.1448864197437732E-3</v>
       </c>
       <c r="AA127">
-        <v>8.5347452430561688E-3</v>
+        <v>8.628025904322394E-3</v>
       </c>
       <c r="AB127">
-        <v>8.900005085750529E-3</v>
+        <v>9.1008586013694749E-3</v>
       </c>
       <c r="AC127">
-        <v>1.1396197296394855E-2</v>
+        <v>1.069827672431382E-2</v>
       </c>
       <c r="AD127">
-        <v>1.0955408078755176E-2</v>
+        <v>1.1742628020026387E-2</v>
       </c>
       <c r="AF127" t="s">
         <v>427</v>
@@ -66420,40 +66420,40 @@
         <v>558</v>
       </c>
       <c r="AH127">
-        <v>2.591915227107108E-2</v>
+        <v>2.5733645014672214E-2</v>
       </c>
       <c r="AI127">
-        <v>2.3689009064202064E-2</v>
+        <v>2.5606921132025996E-2</v>
       </c>
       <c r="AJ127">
-        <v>2.8952070850376856E-2</v>
+        <v>2.6630862960072162E-2</v>
       </c>
       <c r="AK127">
-        <v>2.0904421196243951E-2</v>
+        <v>1.9455765673108083E-2</v>
       </c>
       <c r="AL127">
-        <v>2.831825877658101E-2</v>
+        <v>2.8952451786081905E-2</v>
       </c>
       <c r="AM127">
-        <v>1.8418779365327653E-2</v>
+        <v>2.0589015683559111E-2</v>
       </c>
       <c r="AN127">
-        <v>1.1825602217056747E-2</v>
+        <v>1.1533900435074849E-2</v>
       </c>
       <c r="AO127">
-        <v>1.7658741440760888E-2</v>
+        <v>1.4532322518062408E-2</v>
       </c>
       <c r="AP127">
-        <v>1.2640243665137271E-2</v>
+        <v>1.2302377503571311E-2</v>
       </c>
       <c r="AQ127">
-        <v>1.4166359135690759E-2</v>
+        <v>1.3173825827522424E-2</v>
       </c>
       <c r="AR127">
-        <v>1.7925087837532012E-2</v>
+        <v>1.6996730557809581E-2</v>
       </c>
       <c r="AS127">
-        <v>1.2728243759641062E-2</v>
+        <v>1.2000896870407233E-2</v>
       </c>
       <c r="AU127" t="s">
         <v>427</v>
@@ -66462,79 +66462,79 @@
         <v>559</v>
       </c>
       <c r="AW127">
-        <v>0.10392332041216101</v>
+        <v>0.10014709413888462</v>
       </c>
       <c r="AX127">
-        <v>8.6190779275313267E-2</v>
+        <v>8.3367529990802658E-2</v>
       </c>
       <c r="AY127">
-        <v>8.1978252946997079E-2</v>
+        <v>8.1696594546342649E-2</v>
       </c>
       <c r="AZ127">
-        <v>0.12570620380933634</v>
+        <v>0.12703328026977717</v>
       </c>
       <c r="BA127">
-        <v>0.13200714842925348</v>
+        <v>0.13001186536516662</v>
       </c>
       <c r="BB127">
-        <v>0.12275939399261053</v>
+        <v>0.12319704986297797</v>
       </c>
       <c r="BC127">
-        <v>9.8546921943260937E-2</v>
+        <v>0.10230530066955151</v>
       </c>
       <c r="BD127">
-        <v>9.6768738566262516E-2</v>
+        <v>9.8159240298114403E-2</v>
       </c>
       <c r="BE127">
-        <v>9.979696393190074E-2</v>
+        <v>0.10007023823878768</v>
       </c>
       <c r="BF127">
-        <v>8.6776982079176668E-2</v>
+        <v>8.6577663392951337E-2</v>
       </c>
       <c r="BG127">
-        <v>8.3349789386189657E-2</v>
+        <v>8.6235028785652576E-2</v>
       </c>
       <c r="BH127">
-        <v>8.844309657053441E-2</v>
+        <v>8.8325735617868037E-2</v>
       </c>
       <c r="BR127" t="s">
         <v>427</v>
       </c>
       <c r="BS127">
-        <v>0.46462135059495135</v>
+        <v>0.47786922339289206</v>
       </c>
       <c r="BT127">
-        <v>0.4939179218257006</v>
+        <v>0.50470047704713406</v>
       </c>
       <c r="BU127">
-        <v>0.50146976782274488</v>
+        <v>0.51430249772960934</v>
       </c>
       <c r="BV127">
-        <v>0.46718055288214372</v>
+        <v>0.47529360428331835</v>
       </c>
       <c r="BW127">
-        <v>0.45622482384612101</v>
+        <v>0.46439849307472419</v>
       </c>
       <c r="BX127">
-        <v>0.48125360481071106</v>
+        <v>0.48807040433546989</v>
       </c>
       <c r="BY127">
-        <v>0.58179886165227557</v>
+        <v>0.59560837967006908</v>
       </c>
       <c r="BZ127">
-        <v>0.57973409879220716</v>
+        <v>0.59407531436703742</v>
       </c>
       <c r="CA127">
-        <v>0.5734843147123555</v>
+        <v>0.58574983153951965</v>
       </c>
       <c r="CB127">
-        <v>0.58798905019048009</v>
+        <v>0.60178277069761721</v>
       </c>
       <c r="CC127">
-        <v>0.58691698359842592</v>
+        <v>0.59568741961091476</v>
       </c>
       <c r="CD127">
-        <v>0.59295002059043278</v>
+        <v>0.60330482923084627</v>
       </c>
       <c r="CF127" t="s">
         <v>479</v>
@@ -67872,7 +67872,7 @@
         <v>572</v>
       </c>
       <c r="CI133">
-        <v>0.39997322446225708</v>
+        <v>0.40268242652065778</v>
       </c>
     </row>
     <row r="134" spans="2:87" x14ac:dyDescent="0.45">
@@ -72966,40 +72966,40 @@
         <v>31</v>
       </c>
       <c r="D157">
-        <v>0.25343998968701298</v>
+        <v>0.2468098784314951</v>
       </c>
       <c r="E157">
-        <v>0.25893771956778094</v>
+        <v>0.25672428696870159</v>
       </c>
       <c r="F157">
-        <v>0.22996827023016106</v>
+        <v>0.23102897489915966</v>
       </c>
       <c r="G157">
-        <v>0.26664869962605248</v>
+        <v>0.27018537107750884</v>
       </c>
       <c r="H157">
-        <v>0.26542391370441881</v>
+        <v>0.26960222923688121</v>
       </c>
       <c r="I157">
-        <v>0.2556185283322826</v>
+        <v>0.2519278058640238</v>
       </c>
       <c r="J157">
-        <v>0.16068843956890205</v>
+        <v>0.16365845210204061</v>
       </c>
       <c r="K157">
-        <v>0.18309053912869325</v>
+        <v>0.1885669929504491</v>
       </c>
       <c r="L157">
-        <v>0.16974879673017135</v>
+        <v>0.17586100061295976</v>
       </c>
       <c r="M157">
-        <v>0.21287510284811262</v>
+        <v>0.21480655939385121</v>
       </c>
       <c r="N157">
-        <v>0.21073934830904073</v>
+        <v>0.21065029387668907</v>
       </c>
       <c r="O157">
-        <v>0.18718417437586748</v>
+        <v>0.18798998775142642</v>
       </c>
       <c r="Q157" t="s">
         <v>457</v>
@@ -73008,40 +73008,40 @@
         <v>557</v>
       </c>
       <c r="S157">
-        <v>9.5238068735332901E-3</v>
+        <v>6.787429786203422E-3</v>
       </c>
       <c r="T157">
-        <v>1.4428769174506917E-2</v>
+        <v>1.6834519048430405E-2</v>
       </c>
       <c r="U157">
-        <v>4.2824437308238619E-3</v>
+        <v>4.9002678902343539E-3</v>
       </c>
       <c r="V157">
-        <v>1.1760874285070557E-2</v>
+        <v>1.3670308929138349E-2</v>
       </c>
       <c r="W157">
-        <v>5.8180226460532768E-3</v>
+        <v>5.4964318760652034E-3</v>
       </c>
       <c r="X157">
-        <v>1.0217218855486076E-2</v>
+        <v>9.2133689413109714E-3</v>
       </c>
       <c r="Y157">
-        <v>6.3819716269228376E-3</v>
+        <v>6.7084177921828657E-3</v>
       </c>
       <c r="Z157">
-        <v>8.7851568552293792E-3</v>
+        <v>7.7881603077812655E-3</v>
       </c>
       <c r="AA157">
-        <v>7.6967238938477015E-3</v>
+        <v>6.9071940717125658E-3</v>
       </c>
       <c r="AB157">
-        <v>4.6657431351104983E-3</v>
+        <v>8.6922641887717447E-3</v>
       </c>
       <c r="AC157">
-        <v>6.0332490986714097E-3</v>
+        <v>5.9611710771445541E-3</v>
       </c>
       <c r="AD157">
-        <v>6.9035780752871364E-3</v>
+        <v>5.9646819592729739E-3</v>
       </c>
       <c r="AF157" t="s">
         <v>457</v>
@@ -73050,40 +73050,40 @@
         <v>558</v>
       </c>
       <c r="AH157">
-        <v>7.5082891729807699E-3</v>
+        <v>5.1047609014388314E-3</v>
       </c>
       <c r="AI157">
-        <v>2.5270773320756473E-2</v>
+        <v>2.5842078385448688E-2</v>
       </c>
       <c r="AJ157">
-        <v>1.6589369449491236E-2</v>
+        <v>1.7147070447583821E-2</v>
       </c>
       <c r="AK157">
-        <v>2.4999476530169581E-2</v>
+        <v>2.0109511722459356E-2</v>
       </c>
       <c r="AL157">
-        <v>1.1864061144302544E-2</v>
+        <v>1.4061746599342419E-2</v>
       </c>
       <c r="AM157">
-        <v>7.4308305260773165E-3</v>
+        <v>5.2642777843137662E-3</v>
       </c>
       <c r="AN157">
-        <v>1.1747587009799295E-2</v>
+        <v>9.6122577973523724E-3</v>
       </c>
       <c r="AO157">
-        <v>7.9948934428642135E-3</v>
+        <v>9.194439683301088E-3</v>
       </c>
       <c r="AP157">
-        <v>1.4467499810457285E-2</v>
+        <v>1.5406477105817098E-2</v>
       </c>
       <c r="AQ157">
-        <v>1.0952497606660958E-2</v>
+        <v>9.9320351107157982E-3</v>
       </c>
       <c r="AR157">
-        <v>7.5411878142457919E-3</v>
+        <v>8.9208691414913565E-3</v>
       </c>
       <c r="AS157">
-        <v>6.5916154228793317E-3</v>
+        <v>6.7204499872510976E-3</v>
       </c>
       <c r="AU157" t="s">
         <v>457</v>
@@ -73092,79 +73092,79 @@
         <v>559</v>
       </c>
       <c r="AW157">
-        <v>0.13136356850689601</v>
+        <v>0.13390174930344606</v>
       </c>
       <c r="AX157">
-        <v>9.827896130090355E-2</v>
+        <v>9.1043871644738789E-2</v>
       </c>
       <c r="AY157">
-        <v>0.10562055644629413</v>
+        <v>0.10190290844861555</v>
       </c>
       <c r="AZ157">
-        <v>0.10708519129492892</v>
+        <v>0.10805014173763101</v>
       </c>
       <c r="BA157">
-        <v>0.13663588255633313</v>
+        <v>0.13678241304366634</v>
       </c>
       <c r="BB157">
-        <v>0.12389049323556491</v>
+        <v>0.12482551413472341</v>
       </c>
       <c r="BC157">
-        <v>5.9225539136235836E-2</v>
+        <v>6.2885693754107838E-2</v>
       </c>
       <c r="BD157">
-        <v>7.0275592972597681E-2</v>
+        <v>7.5744153569418493E-2</v>
       </c>
       <c r="BE157">
-        <v>5.6302511197628323E-2</v>
+        <v>5.8850558049167813E-2</v>
       </c>
       <c r="BF157">
-        <v>9.4021883395089226E-2</v>
+        <v>8.6747877141142404E-2</v>
       </c>
       <c r="BG157">
-        <v>9.4159609960808036E-2</v>
+        <v>9.1466086463778587E-2</v>
       </c>
       <c r="BH157">
-        <v>8.624951328110575E-2</v>
+        <v>8.4636245828078452E-2</v>
       </c>
       <c r="BR157" t="s">
         <v>457</v>
       </c>
       <c r="BS157">
-        <v>0.46726017693284416</v>
+        <v>0.46802469897621279</v>
       </c>
       <c r="BT157">
-        <v>0.51013929062361152</v>
+        <v>0.51089470697233696</v>
       </c>
       <c r="BU157">
-        <v>0.5058866547080495</v>
+        <v>0.512683795762921</v>
       </c>
       <c r="BV157">
-        <v>0.51044248813298299</v>
+        <v>0.50380502848034758</v>
       </c>
       <c r="BW157">
-        <v>0.49176006640561326</v>
+        <v>0.48471025121732381</v>
       </c>
       <c r="BX157">
-        <v>0.51036807969135478</v>
+        <v>0.50782662428528236</v>
       </c>
       <c r="BY157">
-        <v>0.64634108111069721</v>
+        <v>0.6342984874184141</v>
       </c>
       <c r="BZ157">
-        <v>0.63528956037244277</v>
+        <v>0.61981263244854035</v>
       </c>
       <c r="CA157">
-        <v>0.63786594918416462</v>
+        <v>0.62824968247851276</v>
       </c>
       <c r="CB157">
-        <v>0.61330054275065371</v>
+        <v>0.61035560830148006</v>
       </c>
       <c r="CC157">
-        <v>0.61662381201785288</v>
+        <v>0.61488327275703081</v>
       </c>
       <c r="CD157">
-        <v>0.63123084393617446</v>
+        <v>0.62926727082777834</v>
       </c>
       <c r="CF157" t="s">
         <v>509</v>
@@ -74292,40 +74292,40 @@
         <v>31</v>
       </c>
       <c r="D163">
-        <v>0.26199381611727729</v>
+        <v>0.2621659936473632</v>
       </c>
       <c r="E163">
-        <v>0.27022254604870161</v>
+        <v>0.27028393682247032</v>
       </c>
       <c r="F163">
-        <v>0.24099646304953459</v>
+        <v>0.2411706695246896</v>
       </c>
       <c r="G163">
-        <v>0.27813411230980589</v>
+        <v>0.27832799605738945</v>
       </c>
       <c r="H163">
-        <v>0.332860453528869</v>
+        <v>0.33304226366544765</v>
       </c>
       <c r="I163">
-        <v>0.30276291061137284</v>
+        <v>0.30312480354928673</v>
       </c>
       <c r="J163">
-        <v>0.27884775565135661</v>
+        <v>0.27882410794351697</v>
       </c>
       <c r="K163">
-        <v>0.27793655340043694</v>
+        <v>0.27771998279806498</v>
       </c>
       <c r="L163">
-        <v>0.25449129335977072</v>
+        <v>0.25444623630773139</v>
       </c>
       <c r="M163">
-        <v>0.22892869030903026</v>
+        <v>0.2294646263703512</v>
       </c>
       <c r="N163">
-        <v>0.25863965505406555</v>
+        <v>0.25888411226034358</v>
       </c>
       <c r="O163">
-        <v>0.22617066545730002</v>
+        <v>0.22658996319805266</v>
       </c>
       <c r="Q163" t="s">
         <v>463</v>
@@ -74334,40 +74334,40 @@
         <v>557</v>
       </c>
       <c r="S163">
-        <v>2.1154568902296476E-2</v>
+        <v>2.1015748064082476E-2</v>
       </c>
       <c r="T163">
-        <v>2.9892171150850834E-2</v>
+        <v>2.9940792935428097E-2</v>
       </c>
       <c r="U163">
-        <v>1.1494076870249153E-2</v>
+        <v>1.1303806260919822E-2</v>
       </c>
       <c r="V163">
-        <v>2.0240826719198204E-2</v>
+        <v>2.0281599624467458E-2</v>
       </c>
       <c r="W163">
-        <v>2.1533579493381957E-2</v>
+        <v>1.9006083658553174E-2</v>
       </c>
       <c r="X163">
-        <v>1.3800432759999587E-2</v>
+        <v>1.3799328219453993E-2</v>
       </c>
       <c r="Y163">
-        <v>1.5977692296327988E-2</v>
+        <v>1.5998679261367568E-2</v>
       </c>
       <c r="Z163">
-        <v>2.0788388651782893E-2</v>
+        <v>2.0357619515437308E-2</v>
       </c>
       <c r="AA163">
-        <v>1.7935734175220423E-2</v>
+        <v>1.7892035970381862E-2</v>
       </c>
       <c r="AB163">
-        <v>1.6343820969478146E-2</v>
+        <v>1.5608078966626211E-2</v>
       </c>
       <c r="AC163">
-        <v>1.4654956978985183E-2</v>
+        <v>1.468810596318906E-2</v>
       </c>
       <c r="AD163">
-        <v>1.2378609837039456E-2</v>
+        <v>1.2396569787590237E-2</v>
       </c>
       <c r="AF163" t="s">
         <v>463</v>
@@ -74376,40 +74376,40 @@
         <v>558</v>
       </c>
       <c r="AH163">
-        <v>2.6421358959355181E-2</v>
+        <v>2.6250511345452986E-2</v>
       </c>
       <c r="AI163">
-        <v>3.2469127211083235E-2</v>
+        <v>3.2758851584053124E-2</v>
       </c>
       <c r="AJ163">
-        <v>3.0453613190716055E-2</v>
+        <v>3.0532758143946622E-2</v>
       </c>
       <c r="AK163">
-        <v>2.3383198666710361E-2</v>
+        <v>2.3551808782164414E-2</v>
       </c>
       <c r="AL163">
-        <v>3.9466043933400051E-2</v>
+        <v>4.1884509940010979E-2</v>
       </c>
       <c r="AM163">
-        <v>1.9980241819695342E-2</v>
+        <v>1.6174007093874183E-2</v>
       </c>
       <c r="AN163">
-        <v>3.3852448843424469E-2</v>
+        <v>3.3954709059028108E-2</v>
       </c>
       <c r="AO163">
-        <v>1.5336128483587418E-2</v>
+        <v>1.5783507135031405E-2</v>
       </c>
       <c r="AP163">
-        <v>3.511028890859319E-2</v>
+        <v>3.3668067701727665E-2</v>
       </c>
       <c r="AQ163">
-        <v>2.1964483193615787E-2</v>
+        <v>2.2483078555008366E-2</v>
       </c>
       <c r="AR163">
-        <v>1.6364114715782131E-2</v>
+        <v>1.6331856972543555E-2</v>
       </c>
       <c r="AS163">
-        <v>1.5884017323714028E-2</v>
+        <v>1.5972003174605426E-2</v>
       </c>
       <c r="AU163" t="s">
         <v>463</v>
@@ -74418,79 +74418,79 @@
         <v>559</v>
       </c>
       <c r="AW163">
-        <v>0.11552581211795851</v>
+        <v>0.11604155199911702</v>
       </c>
       <c r="AX163">
-        <v>0.10347696004616966</v>
+        <v>0.10331471123819605</v>
       </c>
       <c r="AY163">
-        <v>0.10759371894401432</v>
+        <v>0.10804687865328387</v>
       </c>
       <c r="AZ163">
-        <v>0.12297337115430587</v>
+        <v>0.12339813526149472</v>
       </c>
       <c r="BA163">
-        <v>0.14333463517418296</v>
+        <v>0.14370687935679172</v>
       </c>
       <c r="BB163">
-        <v>0.15389879772070827</v>
+        <v>0.15793911484043943</v>
       </c>
       <c r="BC163">
-        <v>0.11327516696359663</v>
+        <v>0.11336315327013492</v>
       </c>
       <c r="BD163">
-        <v>0.12875397623056678</v>
+        <v>0.1287794359254496</v>
       </c>
       <c r="BE163">
-        <v>0.10081332871806832</v>
+        <v>0.10234725021544461</v>
       </c>
       <c r="BF163">
-        <v>9.9629250962459531E-2</v>
+        <v>0.10015966292780193</v>
       </c>
       <c r="BG163">
-        <v>0.12005530434669995</v>
+        <v>0.12009323043165269</v>
       </c>
       <c r="BH163">
-        <v>0.10798920245418762</v>
+        <v>0.10814170285002452</v>
       </c>
       <c r="BR163" t="s">
         <v>463</v>
       </c>
       <c r="BS163">
-        <v>0.32969856454692298</v>
+        <v>0.32833998921954899</v>
       </c>
       <c r="BT163">
-        <v>0.39131565647834304</v>
+        <v>0.3901206341230965</v>
       </c>
       <c r="BU163">
-        <v>0.3569106319314056</v>
+        <v>0.35530803411725909</v>
       </c>
       <c r="BV163">
-        <v>0.33431190447051373</v>
+        <v>0.33342965873684888</v>
       </c>
       <c r="BW163">
-        <v>0.34423440070052891</v>
+        <v>0.34350530766660431</v>
       </c>
       <c r="BX163">
-        <v>0.32907948735777537</v>
+        <v>0.3281398192440767</v>
       </c>
       <c r="BY163">
-        <v>0.41175821636868565</v>
+        <v>0.41102247286241461</v>
       </c>
       <c r="BZ163">
-        <v>0.42431260200755189</v>
+        <v>0.42372001744094606</v>
       </c>
       <c r="CA163">
-        <v>0.41442388427361249</v>
+        <v>0.41348785852327546</v>
       </c>
       <c r="CB163">
-        <v>0.4364513657503773</v>
+        <v>0.43528841967662185</v>
       </c>
       <c r="CC163">
-        <v>0.47178451181428088</v>
+        <v>0.47079389601380189</v>
       </c>
       <c r="CD163">
-        <v>0.44297325976844892</v>
+        <v>0.44192699576091782</v>
       </c>
       <c r="CF163" t="s">
         <v>515</v>
@@ -79154,40 +79154,40 @@
         <v>31</v>
       </c>
       <c r="D185">
-        <v>0.32239210403757196</v>
+        <v>0.31671352787147544</v>
       </c>
       <c r="E185">
-        <v>0.31715746431721897</v>
+        <v>0.31312626835160945</v>
       </c>
       <c r="F185">
-        <v>0.26413234132751506</v>
+        <v>0.25692989735164445</v>
       </c>
       <c r="G185">
-        <v>0.33943953193144949</v>
+        <v>0.3378839736194304</v>
       </c>
       <c r="H185">
-        <v>0.38491185808529099</v>
+        <v>0.38522336221430198</v>
       </c>
       <c r="I185">
-        <v>0.33390618794079996</v>
+        <v>0.33181289046855694</v>
       </c>
       <c r="J185">
-        <v>0.28530820484559644</v>
+        <v>0.2935501202094366</v>
       </c>
       <c r="K185">
-        <v>0.29568664488630653</v>
+        <v>0.29788098640859312</v>
       </c>
       <c r="L185">
-        <v>0.27286353748515413</v>
+        <v>0.27973857578067696</v>
       </c>
       <c r="M185">
-        <v>0.31779288740140244</v>
+        <v>0.31230122535271143</v>
       </c>
       <c r="N185">
-        <v>0.30618695351390401</v>
+        <v>0.30692331237953185</v>
       </c>
       <c r="O185">
-        <v>0.29475954436991836</v>
+        <v>0.29338216309741261</v>
       </c>
       <c r="Q185" t="s">
         <v>485</v>
@@ -79196,40 +79196,40 @@
         <v>557</v>
       </c>
       <c r="S185">
-        <v>1.7875356561983757E-2</v>
+        <v>1.7011281788317789E-2</v>
       </c>
       <c r="T185">
-        <v>2.8399399015155667E-2</v>
+        <v>2.8959211539663576E-2</v>
       </c>
       <c r="U185">
-        <v>1.4751970461099074E-2</v>
+        <v>2.1740365424015886E-2</v>
       </c>
       <c r="V185">
-        <v>2.6862371176105074E-2</v>
+        <v>2.552628757805183E-2</v>
       </c>
       <c r="W185">
-        <v>1.6767895124965664E-2</v>
+        <v>1.9657876766394584E-2</v>
       </c>
       <c r="X185">
-        <v>8.663136434983152E-3</v>
+        <v>8.2774335563694131E-3</v>
       </c>
       <c r="Y185">
-        <v>2.4517043153903167E-2</v>
+        <v>2.1063941097627995E-2</v>
       </c>
       <c r="Z185">
-        <v>1.8689439665984568E-2</v>
+        <v>1.7279799161362019E-2</v>
       </c>
       <c r="AA185">
-        <v>2.3728432327071683E-2</v>
+        <v>2.5856164413134493E-2</v>
       </c>
       <c r="AB185">
-        <v>1.2256021190505067E-2</v>
+        <v>1.3021064160354002E-2</v>
       </c>
       <c r="AC185">
-        <v>1.9858007183836415E-2</v>
+        <v>1.9359833857630761E-2</v>
       </c>
       <c r="AD185">
-        <v>1.6229599239770087E-2</v>
+        <v>1.5242948692408333E-2</v>
       </c>
       <c r="AF185" t="s">
         <v>485</v>
@@ -79238,40 +79238,40 @@
         <v>558</v>
       </c>
       <c r="AH185">
-        <v>2.1868138418905097E-2</v>
+        <v>2.3799873761417237E-2</v>
       </c>
       <c r="AI185">
-        <v>4.0610238116728446E-2</v>
+        <v>4.2298737845634128E-2</v>
       </c>
       <c r="AJ185">
-        <v>3.8700508973388989E-2</v>
+        <v>3.5793514560968874E-2</v>
       </c>
       <c r="AK185">
-        <v>2.8151649254220534E-2</v>
+        <v>2.9037096029893166E-2</v>
       </c>
       <c r="AL185">
-        <v>3.9699364051611508E-2</v>
+        <v>3.9986937931437906E-2</v>
       </c>
       <c r="AM185">
-        <v>1.7460148935234839E-2</v>
+        <v>2.0886698939688537E-2</v>
       </c>
       <c r="AN185">
-        <v>3.3145568757127798E-2</v>
+        <v>4.3890130266712693E-2</v>
       </c>
       <c r="AO185">
-        <v>2.6837140837071862E-2</v>
+        <v>2.4353128771386394E-2</v>
       </c>
       <c r="AP185">
-        <v>3.3888934359517099E-2</v>
+        <v>3.2158958842269617E-2</v>
       </c>
       <c r="AQ185">
-        <v>3.3771460721856397E-2</v>
+        <v>3.1479786627783578E-2</v>
       </c>
       <c r="AR185">
-        <v>2.0317601101097923E-2</v>
+        <v>2.2798796368272194E-2</v>
       </c>
       <c r="AS185">
-        <v>3.3598776069232214E-2</v>
+        <v>3.4456337791489773E-2</v>
       </c>
       <c r="AU185" t="s">
         <v>485</v>
@@ -79280,79 +79280,79 @@
         <v>559</v>
       </c>
       <c r="AW185">
-        <v>0.16782382298410908</v>
+        <v>0.16541326573238374</v>
       </c>
       <c r="AX185">
-        <v>0.14054946488079764</v>
+        <v>0.13396584595130664</v>
       </c>
       <c r="AY185">
-        <v>0.11578916558497822</v>
+        <v>0.10638906262734271</v>
       </c>
       <c r="AZ185">
-        <v>0.17279859488348831</v>
+        <v>0.17312867550466648</v>
       </c>
       <c r="BA185">
-        <v>0.20917779827903279</v>
+        <v>0.20240683235648718</v>
       </c>
       <c r="BB185">
-        <v>0.19951327903549523</v>
+        <v>0.19573184488105305</v>
       </c>
       <c r="BC185">
-        <v>0.12409857123109984</v>
+        <v>0.1208965319932831</v>
       </c>
       <c r="BD185">
-        <v>0.14035546885745515</v>
+        <v>0.14490329309880823</v>
       </c>
       <c r="BE185">
-        <v>0.11259382444852388</v>
+        <v>0.114507075483146</v>
       </c>
       <c r="BF185">
-        <v>0.15890523212575497</v>
+        <v>0.15795425693978166</v>
       </c>
       <c r="BG185">
-        <v>0.15081854778547657</v>
+        <v>0.14786522943039987</v>
       </c>
       <c r="BH185">
-        <v>0.13395142297880461</v>
+        <v>0.13264766007504644</v>
       </c>
       <c r="BR185" t="s">
         <v>485</v>
       </c>
       <c r="BS185">
-        <v>0.21472364282074596</v>
+        <v>0.21846216642044652</v>
       </c>
       <c r="BT185">
-        <v>0.3025780551378342</v>
+        <v>0.3040133185578866</v>
       </c>
       <c r="BU185">
-        <v>0.25910207146860403</v>
+        <v>0.26400128388648925</v>
       </c>
       <c r="BV185">
-        <v>0.24052229626115937</v>
+        <v>0.24106331838900938</v>
       </c>
       <c r="BW185">
-        <v>0.27762811306803975</v>
+        <v>0.27888974096880315</v>
       </c>
       <c r="BX185">
-        <v>0.25931049101864456</v>
+        <v>0.26240717754686521</v>
       </c>
       <c r="BY185">
-        <v>0.35062866038657342</v>
+        <v>0.35793817223030577</v>
       </c>
       <c r="BZ185">
-        <v>0.36500731828574706</v>
+        <v>0.37420294874043347</v>
       </c>
       <c r="CA185">
-        <v>0.33593190431979325</v>
+        <v>0.34487360388083355</v>
       </c>
       <c r="CB185">
-        <v>0.34074034861820773</v>
+        <v>0.34401118210129072</v>
       </c>
       <c r="CC185">
-        <v>0.40311220523629426</v>
+        <v>0.4058729952428442</v>
       </c>
       <c r="CD185">
-        <v>0.35905528015545035</v>
+        <v>0.36332776028512886</v>
       </c>
       <c r="CF185" t="s">
         <v>537</v>
@@ -81795,7 +81795,7 @@
         <v>572</v>
       </c>
       <c r="CI196">
-        <v>0.39090653010175208</v>
+        <v>0.38997180786764685</v>
       </c>
     </row>
     <row r="197" spans="2:87" x14ac:dyDescent="0.45">
@@ -84226,7 +84226,7 @@
         <v>572</v>
       </c>
       <c r="CI207">
-        <v>0.63565391591979048</v>
+        <v>0.62855232427025265</v>
       </c>
     </row>
     <row r="208" spans="2:87" x14ac:dyDescent="0.45">
@@ -84447,7 +84447,7 @@
         <v>572</v>
       </c>
       <c r="CI208">
-        <v>0.63778710466841904</v>
+        <v>0.63373296967613568</v>
       </c>
     </row>
     <row r="209" spans="2:87" x14ac:dyDescent="0.45">
@@ -87983,7 +87983,7 @@
         <v>572</v>
       </c>
       <c r="CI224">
-        <v>0.58016572356529938</v>
+        <v>0.58822332136602828</v>
       </c>
     </row>
     <row r="225" spans="2:87" x14ac:dyDescent="0.45">
@@ -93077,40 +93077,40 @@
         <v>31</v>
       </c>
       <c r="D248">
-        <v>0.3597364407410753</v>
+        <v>0.36845772859580728</v>
       </c>
       <c r="E248">
-        <v>0.33700650229803608</v>
+        <v>0.34750970452020097</v>
       </c>
       <c r="F248">
-        <v>0.32254319005388599</v>
+        <v>0.32568393272090268</v>
       </c>
       <c r="G248">
-        <v>0.35971896859165775</v>
+        <v>0.35843930008289143</v>
       </c>
       <c r="H248">
-        <v>0.4009270032821593</v>
+        <v>0.40484489566767751</v>
       </c>
       <c r="I248">
-        <v>0.36759809560270035</v>
+        <v>0.35938042002990733</v>
       </c>
       <c r="J248">
-        <v>0.26656050233718953</v>
+        <v>0.27581062038196763</v>
       </c>
       <c r="K248">
-        <v>0.2968855017763678</v>
+        <v>0.31061174044059053</v>
       </c>
       <c r="L248">
-        <v>0.26566017268178138</v>
+        <v>0.2721796230934676</v>
       </c>
       <c r="M248">
-        <v>0.33421296933785949</v>
+        <v>0.3559245641863627</v>
       </c>
       <c r="N248">
-        <v>0.30931835588611006</v>
+        <v>0.32515116828608637</v>
       </c>
       <c r="O248">
-        <v>0.31019856868314977</v>
+        <v>0.31796872543549276</v>
       </c>
       <c r="Q248" t="s">
         <v>548</v>
@@ -93119,40 +93119,40 @@
         <v>557</v>
       </c>
       <c r="S248">
-        <v>1.8250110213243374E-2</v>
+        <v>3.463100136094472E-2</v>
       </c>
       <c r="T248">
-        <v>3.8418835699264485E-2</v>
+        <v>3.7644685102914424E-2</v>
       </c>
       <c r="U248">
-        <v>1.1281486243418314E-2</v>
+        <v>1.9793164942804722E-2</v>
       </c>
       <c r="V248">
-        <v>2.8109254293636091E-2</v>
+        <v>3.1153394903374858E-2</v>
       </c>
       <c r="W248">
-        <v>1.4049585892573362E-2</v>
+        <v>1.8687104292476171E-2</v>
       </c>
       <c r="X248">
-        <v>6.7306103017149921E-3</v>
+        <v>8.707196594834132E-3</v>
       </c>
       <c r="Y248">
-        <v>3.7801089292561721E-2</v>
+        <v>3.4202966462681256E-2</v>
       </c>
       <c r="Z248">
-        <v>2.5051812562650239E-2</v>
+        <v>2.9586205203477565E-2</v>
       </c>
       <c r="AA248">
-        <v>1.6622292289965351E-2</v>
+        <v>2.4661231303614414E-2</v>
       </c>
       <c r="AB248">
-        <v>1.2407204297339512E-2</v>
+        <v>1.6926682900450997E-2</v>
       </c>
       <c r="AC248">
-        <v>1.2939055234520091E-2</v>
+        <v>2.1068304559208589E-2</v>
       </c>
       <c r="AD248">
-        <v>1.8321439067304615E-2</v>
+        <v>2.2207165417686081E-2</v>
       </c>
       <c r="AF248" t="s">
         <v>548</v>
@@ -93161,40 +93161,40 @@
         <v>558</v>
       </c>
       <c r="AH248">
-        <v>2.3718547412658251E-2</v>
+        <v>2.741894498881229E-2</v>
       </c>
       <c r="AI248">
-        <v>4.4435714097412315E-2</v>
+        <v>4.5325053141524324E-2</v>
       </c>
       <c r="AJ248">
-        <v>3.7595944641594325E-2</v>
+        <v>4.6939421167578939E-2</v>
       </c>
       <c r="AK248">
-        <v>2.3101867381728574E-2</v>
+        <v>2.7775006639390306E-2</v>
       </c>
       <c r="AL248">
-        <v>3.7960609318205059E-2</v>
+        <v>3.8851521751781935E-2</v>
       </c>
       <c r="AM248">
-        <v>1.0284342087092698E-2</v>
+        <v>1.2378450892989371E-2</v>
       </c>
       <c r="AN248">
-        <v>2.7083407379668342E-2</v>
+        <v>3.7405201633524655E-2</v>
       </c>
       <c r="AO248">
-        <v>2.9689228324666861E-2</v>
+        <v>3.6076064014740852E-2</v>
       </c>
       <c r="AP248">
-        <v>4.0895514160011165E-2</v>
+        <v>3.6839118881408631E-2</v>
       </c>
       <c r="AQ248">
-        <v>2.6147920872014573E-2</v>
+        <v>3.3293813802872031E-2</v>
       </c>
       <c r="AR248">
-        <v>2.03558135270825E-2</v>
+        <v>1.9668251090377942E-2</v>
       </c>
       <c r="AS248">
-        <v>2.7579313492049087E-2</v>
+        <v>3.0487974034113161E-2</v>
       </c>
       <c r="AU248" t="s">
         <v>548</v>
@@ -93203,79 +93203,79 @@
         <v>559</v>
       </c>
       <c r="AW248">
-        <v>0.19488026828255869</v>
+        <v>0.17733728504659091</v>
       </c>
       <c r="AX248">
-        <v>0.12546222172946711</v>
+        <v>0.14547694675590764</v>
       </c>
       <c r="AY248">
-        <v>0.1600019530380021</v>
+        <v>0.15309260682578757</v>
       </c>
       <c r="AZ248">
-        <v>0.18059425463067522</v>
+        <v>0.17406112077422389</v>
       </c>
       <c r="BA248">
-        <v>0.22559630136545636</v>
+        <v>0.22804977234395107</v>
       </c>
       <c r="BB248">
-        <v>0.23116173153812436</v>
+        <v>0.22042317708264825</v>
       </c>
       <c r="BC248">
-        <v>0.10481786377137109</v>
+        <v>0.10357817930760956</v>
       </c>
       <c r="BD248">
-        <v>0.12405499631800067</v>
+        <v>0.12510898168719767</v>
       </c>
       <c r="BE248">
-        <v>0.10859764951788461</v>
+        <v>0.10836532767464373</v>
       </c>
       <c r="BF248">
-        <v>0.16246807050080772</v>
+        <v>0.16914866197956127</v>
       </c>
       <c r="BG248">
-        <v>0.15023790936443501</v>
+        <v>0.15888592322443518</v>
       </c>
       <c r="BH248">
-        <v>0.14923950185617105</v>
+        <v>0.14941725600009911</v>
       </c>
       <c r="BR248" t="s">
         <v>548</v>
       </c>
       <c r="BS248">
-        <v>0.2123579677551698</v>
+        <v>0.20406104932895133</v>
       </c>
       <c r="BT248">
-        <v>0.30730668869162225</v>
+        <v>0.30001272974990811</v>
       </c>
       <c r="BU248">
-        <v>0.25639244792803134</v>
+        <v>0.24570943992597238</v>
       </c>
       <c r="BV248">
-        <v>0.24808953897340619</v>
+        <v>0.24060935369687292</v>
       </c>
       <c r="BW248">
-        <v>0.28004183695458168</v>
+        <v>0.27472947892159438</v>
       </c>
       <c r="BX248">
-        <v>0.25458431566849071</v>
+        <v>0.24995449339550399</v>
       </c>
       <c r="BY248">
-        <v>0.32046155689636652</v>
+        <v>0.32373200710081085</v>
       </c>
       <c r="BZ248">
-        <v>0.33614920592961578</v>
+        <v>0.33309155607270985</v>
       </c>
       <c r="CA248">
-        <v>0.31256448590136893</v>
+        <v>0.30614168166389932</v>
       </c>
       <c r="CB248">
-        <v>0.34519708766015789</v>
+        <v>0.33294886851474714</v>
       </c>
       <c r="CC248">
-        <v>0.39637500425512628</v>
+        <v>0.39429087792836814</v>
       </c>
       <c r="CD248">
-        <v>0.35804294775871021</v>
+        <v>0.34727363772383613</v>
       </c>
       <c r="CF248" t="s">
         <v>451</v>
@@ -94613,7 +94613,7 @@
         <v>572</v>
       </c>
       <c r="CI254">
-        <v>0.63070120386139772</v>
+        <v>0.62498178906307145</v>
       </c>
     </row>
     <row r="255" spans="2:87" x14ac:dyDescent="0.45">
@@ -95064,7 +95064,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71B01E6F-2D4A-4DBE-9D7B-73192C26163E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB73D2E9-88C4-4261-9BB8-9D4CABF242D2}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -95332,7 +95332,7 @@
         <v>38</v>
       </c>
       <c r="R15">
-        <v>0.18506666666666668</v>
+        <v>0.18506666666666663</v>
       </c>
       <c r="S15" t="s">
         <v>586</v>
@@ -95537,7 +95537,7 @@
         <v>42</v>
       </c>
       <c r="R20">
-        <v>0.24216666666666672</v>
+        <v>0.24216666666666667</v>
       </c>
       <c r="S20" t="s">
         <v>586</v>
@@ -95639,7 +95639,7 @@
         <v>38</v>
       </c>
       <c r="R23">
-        <v>0.22023333333333331</v>
+        <v>0.22023333333333336</v>
       </c>
       <c r="S23" t="s">
         <v>586</v>
@@ -95719,7 +95719,7 @@
         <v>38</v>
       </c>
       <c r="R27">
-        <v>0.18723333333333336</v>
+        <v>0.18723333333333333</v>
       </c>
       <c r="S27" t="s">
         <v>586</v>
@@ -95799,7 +95799,7 @@
         <v>38</v>
       </c>
       <c r="R31">
-        <v>0.17966666666666667</v>
+        <v>0.17966666666666664</v>
       </c>
       <c r="S31" t="s">
         <v>586</v>
@@ -95943,7 +95943,7 @@
         <v>42</v>
       </c>
       <c r="R40">
-        <v>0.21413333333333337</v>
+        <v>0.21413333333333331</v>
       </c>
       <c r="S40" t="s">
         <v>586</v>
@@ -95985,7 +95985,7 @@
         <v>38</v>
       </c>
       <c r="R43">
-        <v>0.20276666666666665</v>
+        <v>0.20276666666666668</v>
       </c>
       <c r="S43" t="s">
         <v>586</v>
@@ -96055,7 +96055,7 @@
         <v>42</v>
       </c>
       <c r="R48">
-        <v>0.1966</v>
+        <v>0.19660000000000002</v>
       </c>
       <c r="S48" t="s">
         <v>586</v>
@@ -96153,7 +96153,7 @@
         <v>38</v>
       </c>
       <c r="R55">
-        <v>0.21196666666666664</v>
+        <v>0.21196666666666666</v>
       </c>
       <c r="S55" t="s">
         <v>586</v>
@@ -96279,7 +96279,7 @@
         <v>42</v>
       </c>
       <c r="R64">
-        <v>0.2127</v>
+        <v>0.21269999999999997</v>
       </c>
       <c r="S64" t="s">
         <v>586</v>
@@ -96377,7 +96377,7 @@
         <v>38</v>
       </c>
       <c r="R71">
-        <v>0.20263333333333333</v>
+        <v>0.20263333333333336</v>
       </c>
       <c r="S71" t="s">
         <v>586</v>
@@ -96447,7 +96447,7 @@
         <v>42</v>
       </c>
       <c r="R76">
-        <v>0.28030000000000005</v>
+        <v>0.28029999999999999</v>
       </c>
       <c r="S76" t="s">
         <v>586</v>
@@ -96545,7 +96545,7 @@
         <v>38</v>
       </c>
       <c r="R83">
-        <v>0.18456666666666668</v>
+        <v>0.18456666666666666</v>
       </c>
       <c r="S83" t="s">
         <v>586</v>
@@ -96657,7 +96657,7 @@
         <v>38</v>
       </c>
       <c r="R91">
-        <v>0.23163333333333333</v>
+        <v>0.23163333333333336</v>
       </c>
       <c r="S91" t="s">
         <v>586</v>
@@ -96671,7 +96671,7 @@
         <v>42</v>
       </c>
       <c r="R92">
-        <v>0.20149999999999998</v>
+        <v>0.20150000000000001</v>
       </c>
       <c r="S92" t="s">
         <v>586</v>
@@ -96727,7 +96727,7 @@
         <v>42</v>
       </c>
       <c r="R96">
-        <v>0.20250000000000001</v>
+        <v>0.20249999999999999</v>
       </c>
       <c r="S96" t="s">
         <v>586</v>
@@ -96881,7 +96881,7 @@
         <v>38</v>
       </c>
       <c r="R107">
-        <v>0.17253333333333334</v>
+        <v>0.17253333333333332</v>
       </c>
       <c r="S107" t="s">
         <v>586</v>
@@ -97049,7 +97049,7 @@
         <v>38</v>
       </c>
       <c r="R119">
-        <v>0.23606666666666665</v>
+        <v>0.23606666666666667</v>
       </c>
       <c r="S119" t="s">
         <v>586</v>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B839A2D-391F-496E-ACE3-E8588B205167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79AD3AE8-DF5A-4CEA-B095-352BA0FE9CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1770,13 +1770,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S4aH2,S2aH2,S3aH2,S1aH2</t>
+    <t>S4aH2,S3aH2,S2aH2,S1aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S3aH1,S2aH1,S3aH3,S4aH1,S1aH1,S4aH3,S2aH3,S1aH3</t>
+    <t>S2aH1,S3aH3,S4aH1,S1aH1,S4aH3,S3aH1,S2aH3,S1aH3</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S3aH1,S2aH1,S3aH3,S4aH1,S1aH1,S4aH3,S2aH3,S1aH3</v>
+        <v>S2aH1,S3aH3,S4aH1,S1aH1,S4aH3,S3aH1,S2aH3,S1aH3</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S4aH2,S2aH2,S3aH2,S1aH2</v>
+        <v>S4aH2,S3aH2,S2aH2,S1aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -2501,7 +2501,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{473B843B-D87B-4A05-94FD-EF58B3B046C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{053AE14C-516E-48A6-B071-B6E96CFA514A}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2581,7 +2581,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{061F0C25-334A-469B-AA45-C70798E8B435}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4D3FEF4-9DDF-4B53-B089-9292A6D06278}">
   <dimension ref="B9:O1174"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -40395,7 +40395,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE32A016-4678-4064-BBEA-1D89BC8CC346}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88546E2B-EEFC-4A3A-9049-A3F763058FBF}">
   <dimension ref="B9:CI256"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -95064,7 +95064,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17FEB260-98FD-49FB-BDA8-7E9FC3D1DDB1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13B682E4-7759-4D4C-BAA7-EE850798E825}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -95332,7 +95332,7 @@
         <v>38</v>
       </c>
       <c r="R15">
-        <v>0.18506666666666668</v>
+        <v>0.18506666666666663</v>
       </c>
       <c r="S15" t="s">
         <v>586</v>
@@ -95537,7 +95537,7 @@
         <v>42</v>
       </c>
       <c r="R20">
-        <v>0.24216666666666667</v>
+        <v>0.24216666666666672</v>
       </c>
       <c r="S20" t="s">
         <v>586</v>
@@ -95719,7 +95719,7 @@
         <v>38</v>
       </c>
       <c r="R27">
-        <v>0.18723333333333336</v>
+        <v>0.18723333333333333</v>
       </c>
       <c r="S27" t="s">
         <v>586</v>
@@ -95943,7 +95943,7 @@
         <v>42</v>
       </c>
       <c r="R40">
-        <v>0.21413333333333331</v>
+        <v>0.21413333333333337</v>
       </c>
       <c r="S40" t="s">
         <v>586</v>
@@ -95985,7 +95985,7 @@
         <v>38</v>
       </c>
       <c r="R43">
-        <v>0.20276666666666665</v>
+        <v>0.20276666666666668</v>
       </c>
       <c r="S43" t="s">
         <v>586</v>
@@ -96055,7 +96055,7 @@
         <v>42</v>
       </c>
       <c r="R48">
-        <v>0.19660000000000002</v>
+        <v>0.1966</v>
       </c>
       <c r="S48" t="s">
         <v>586</v>
@@ -96097,7 +96097,7 @@
         <v>38</v>
       </c>
       <c r="R51">
-        <v>0.19266666666666665</v>
+        <v>0.19266666666666668</v>
       </c>
       <c r="S51" t="s">
         <v>586</v>
@@ -96279,7 +96279,7 @@
         <v>42</v>
       </c>
       <c r="R64">
-        <v>0.21269999999999997</v>
+        <v>0.2127</v>
       </c>
       <c r="S64" t="s">
         <v>586</v>
@@ -96377,7 +96377,7 @@
         <v>38</v>
       </c>
       <c r="R71">
-        <v>0.20263333333333333</v>
+        <v>0.20263333333333336</v>
       </c>
       <c r="S71" t="s">
         <v>586</v>
@@ -96447,7 +96447,7 @@
         <v>42</v>
       </c>
       <c r="R76">
-        <v>0.28029999999999999</v>
+        <v>0.28030000000000005</v>
       </c>
       <c r="S76" t="s">
         <v>586</v>
@@ -96545,7 +96545,7 @@
         <v>38</v>
       </c>
       <c r="R83">
-        <v>0.18456666666666668</v>
+        <v>0.18456666666666666</v>
       </c>
       <c r="S83" t="s">
         <v>586</v>
@@ -96657,7 +96657,7 @@
         <v>38</v>
       </c>
       <c r="R91">
-        <v>0.23163333333333333</v>
+        <v>0.23163333333333336</v>
       </c>
       <c r="S91" t="s">
         <v>586</v>
@@ -96671,7 +96671,7 @@
         <v>42</v>
       </c>
       <c r="R92">
-        <v>0.20150000000000001</v>
+        <v>0.20149999999999998</v>
       </c>
       <c r="S92" t="s">
         <v>586</v>
@@ -96727,7 +96727,7 @@
         <v>42</v>
       </c>
       <c r="R96">
-        <v>0.20249999999999999</v>
+        <v>0.20250000000000001</v>
       </c>
       <c r="S96" t="s">
         <v>586</v>
@@ -96769,7 +96769,7 @@
         <v>38</v>
       </c>
       <c r="R99">
-        <v>0.19093333333333332</v>
+        <v>0.19093333333333337</v>
       </c>
       <c r="S99" t="s">
         <v>586</v>
@@ -96881,7 +96881,7 @@
         <v>38</v>
       </c>
       <c r="R107">
-        <v>0.17253333333333334</v>
+        <v>0.17253333333333332</v>
       </c>
       <c r="S107" t="s">
         <v>586</v>
@@ -97049,7 +97049,7 @@
         <v>38</v>
       </c>
       <c r="R119">
-        <v>0.23606666666666665</v>
+        <v>0.23606666666666667</v>
       </c>
       <c r="S119" t="s">
         <v>586</v>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79AD3AE8-DF5A-4CEA-B095-352BA0FE9CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F9AEDC-6E6A-42A6-9E7E-9FF7793E1755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1770,13 +1770,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S4aH2,S3aH2,S2aH2,S1aH2</t>
+    <t>S1aH2,S2aH2,S3aH2,S4aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S2aH1,S3aH3,S4aH1,S1aH1,S4aH3,S3aH1,S2aH3,S1aH3</t>
+    <t>S2aH3,S1aH3,S1aH1,S4aH3,S3aH3,S4aH1,S3aH1,S2aH1</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S2aH1,S3aH3,S4aH1,S1aH1,S4aH3,S3aH1,S2aH3,S1aH3</v>
+        <v>S2aH3,S1aH3,S1aH1,S4aH3,S3aH3,S4aH1,S3aH1,S2aH1</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S4aH2,S3aH2,S2aH2,S1aH2</v>
+        <v>S1aH2,S2aH2,S3aH2,S4aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -2501,7 +2501,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{053AE14C-516E-48A6-B071-B6E96CFA514A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BB860DD-C074-42B7-9DC6-8EA28295CD92}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2581,7 +2581,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4D3FEF4-9DDF-4B53-B089-9292A6D06278}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{033B1302-70DF-4938-AE66-5E804D76574F}">
   <dimension ref="B9:O1174"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -40395,7 +40395,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88546E2B-EEFC-4A3A-9049-A3F763058FBF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C942DFD9-09C5-4AB1-B3AF-4A8EFB17FBB9}">
   <dimension ref="B9:CI256"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -95064,7 +95064,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13B682E4-7759-4D4C-BAA7-EE850798E825}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0298E993-C753-4773-BC78-99F366CA9C00}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -95414,7 +95414,7 @@
         <v>44</v>
       </c>
       <c r="R17">
-        <v>0.27526666666666672</v>
+        <v>0.27526666666666666</v>
       </c>
       <c r="S17" t="s">
         <v>586</v>
@@ -95537,7 +95537,7 @@
         <v>42</v>
       </c>
       <c r="R20">
-        <v>0.24216666666666672</v>
+        <v>0.24216666666666667</v>
       </c>
       <c r="S20" t="s">
         <v>586</v>
@@ -95943,7 +95943,7 @@
         <v>42</v>
       </c>
       <c r="R40">
-        <v>0.21413333333333337</v>
+        <v>0.21413333333333331</v>
       </c>
       <c r="S40" t="s">
         <v>586</v>
@@ -96013,7 +96013,7 @@
         <v>44</v>
       </c>
       <c r="R45">
-        <v>0.29126666666666662</v>
+        <v>0.29126666666666667</v>
       </c>
       <c r="S45" t="s">
         <v>586</v>
@@ -96055,7 +96055,7 @@
         <v>42</v>
       </c>
       <c r="R48">
-        <v>0.1966</v>
+        <v>0.19660000000000002</v>
       </c>
       <c r="S48" t="s">
         <v>586</v>
@@ -96279,7 +96279,7 @@
         <v>42</v>
       </c>
       <c r="R64">
-        <v>0.2127</v>
+        <v>0.21269999999999997</v>
       </c>
       <c r="S64" t="s">
         <v>586</v>
@@ -96447,7 +96447,7 @@
         <v>42</v>
       </c>
       <c r="R76">
-        <v>0.28030000000000005</v>
+        <v>0.28029999999999999</v>
       </c>
       <c r="S76" t="s">
         <v>586</v>
@@ -96461,7 +96461,7 @@
         <v>44</v>
       </c>
       <c r="R77">
-        <v>0.32863333333333333</v>
+        <v>0.32863333333333339</v>
       </c>
       <c r="S77" t="s">
         <v>586</v>
@@ -96517,7 +96517,7 @@
         <v>44</v>
       </c>
       <c r="R81">
-        <v>0.26493333333333335</v>
+        <v>0.2649333333333333</v>
       </c>
       <c r="S81" t="s">
         <v>586</v>
@@ -96629,7 +96629,7 @@
         <v>44</v>
       </c>
       <c r="R89">
-        <v>0.31253333333333333</v>
+        <v>0.31253333333333339</v>
       </c>
       <c r="S89" t="s">
         <v>586</v>
@@ -96671,7 +96671,7 @@
         <v>42</v>
       </c>
       <c r="R92">
-        <v>0.20149999999999998</v>
+        <v>0.20150000000000001</v>
       </c>
       <c r="S92" t="s">
         <v>586</v>
@@ -96685,7 +96685,7 @@
         <v>44</v>
       </c>
       <c r="R93">
-        <v>0.26846666666666669</v>
+        <v>0.26846666666666663</v>
       </c>
       <c r="S93" t="s">
         <v>586</v>
@@ -96727,7 +96727,7 @@
         <v>42</v>
       </c>
       <c r="R96">
-        <v>0.20250000000000001</v>
+        <v>0.20249999999999999</v>
       </c>
       <c r="S96" t="s">
         <v>586</v>
@@ -96741,7 +96741,7 @@
         <v>44</v>
       </c>
       <c r="R97">
-        <v>0.32883333333333337</v>
+        <v>0.32883333333333331</v>
       </c>
       <c r="S97" t="s">
         <v>586</v>
@@ -96965,7 +96965,7 @@
         <v>44</v>
       </c>
       <c r="R113">
-        <v>0.32246666666666668</v>
+        <v>0.32246666666666662</v>
       </c>
       <c r="S113" t="s">
         <v>586</v>
